--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -957,15 +957,15 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · "&amp;Config!B5</f>
-        <v/>
+        <v>Prisma Comunicação (exemplo fictício) · 3º trimestre de 2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6">
+      <c r="A2" s="6" t="str">
         <f>"Semana "&amp;Config!B9&amp;" de 13 · "&amp;TEXT(Config!B10,"0%")&amp;" do trimestre decorrido. Nada para preencher aqui."</f>
-        <v/>
+        <v>Semana 12 de 13 · 86% do trimestre decorrido. Nada para preencher aqui.</v>
       </c>
     </row>
     <row r="4">
@@ -997,22 +997,22 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>COUNTIFS(Metas!$B$5:$B$24,"&lt;&gt;")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>COUNTIFS(Metas!$J$5:$J$24,"Atingido")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>COUNTIFS(Metas!$J$5:$J$24,"Em risco")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>IFERROR(AVERAGEIFS(Metas!$H$5:$H$24,Metas!$B$5:$B$24,"&lt;&gt;"),0)</f>
-        <v/>
+        <v>0.646296296296296</v>
       </c>
       <c r="H5" s="14" t="n"/>
     </row>
@@ -1058,113 +1058,113 @@
       <c r="H8" s="22" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="23">
+      <c r="A9" s="23" t="str">
         <f>IF(Metas!$A$5="","",Metas!$A$5)</f>
-        <v/>
+        <v>Crescer a receita recorrente</v>
       </c>
       <c r="B9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$B$5:$B$8,"&lt;&gt;"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C9" s="25">
         <f>IF(OR(Metas!$A$5="",B9=0),"",AVERAGEIFS(Metas!$H$5:$H$8,Metas!$B$5:$B$8,"&lt;&gt;"))</f>
-        <v/>
+        <v>0.816666666666667</v>
       </c>
       <c r="D9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$J$5:$J$8,"Atingido"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$J$5:$J$8,"Em risco"))</f>
-        <v/>
-      </c>
-      <c r="F9" s="26">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26" t="str">
         <f>IF(C9="","",REPT("█",ROUND(C9*30,0)))</f>
-        <v/>
+        <v>█████████████████████████</v>
       </c>
       <c r="G9" s="21" t="n"/>
       <c r="H9" s="22" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="23">
+      <c r="A10" s="23" t="str">
         <f>IF(Metas!$A$9="","",Metas!$A$9)</f>
-        <v/>
+        <v>Entregar no prazo</v>
       </c>
       <c r="B10" s="24">
         <f>IF(Metas!$A$9="","",COUNTIFS(Metas!$B$9:$B$12,"&lt;&gt;"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C10" s="25">
         <f>IF(OR(Metas!$A$9="",B10=0),"",AVERAGEIFS(Metas!$H$9:$H$12,Metas!$B$9:$B$12,"&lt;&gt;"))</f>
-        <v/>
+        <v>0.533333333333333</v>
       </c>
       <c r="D10" s="24">
         <f>IF(Metas!$A$9="","",COUNTIFS(Metas!$J$9:$J$12,"Atingido"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E10" s="24">
         <f>IF(Metas!$A$9="","",COUNTIFS(Metas!$J$9:$J$12,"Em risco"))</f>
-        <v/>
-      </c>
-      <c r="F10" s="26">
+        <v>1</v>
+      </c>
+      <c r="F10" s="26" t="str">
         <f>IF(C10="","",REPT("█",ROUND(C10*30,0)))</f>
-        <v/>
+        <v>████████████████</v>
       </c>
       <c r="G10" s="21" t="n"/>
       <c r="H10" s="22" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="23">
+      <c r="A11" s="23" t="str">
         <f>IF(Metas!$A$13="","",Metas!$A$13)</f>
-        <v/>
+        <v>Reduzir retrabalho</v>
       </c>
       <c r="B11" s="24">
         <f>IF(Metas!$A$13="","",COUNTIFS(Metas!$B$13:$B$16,"&lt;&gt;"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C11" s="25">
         <f>IF(OR(Metas!$A$13="",B11=0),"",AVERAGEIFS(Metas!$H$13:$H$16,Metas!$B$13:$B$16,"&lt;&gt;"))</f>
-        <v/>
+        <v>0.566666666666667</v>
       </c>
       <c r="D11" s="24">
         <f>IF(Metas!$A$13="","",COUNTIFS(Metas!$J$13:$J$16,"Atingido"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E11" s="24">
         <f>IF(Metas!$A$13="","",COUNTIFS(Metas!$J$13:$J$16,"Em risco"))</f>
-        <v/>
-      </c>
-      <c r="F11" s="26">
+        <v>1</v>
+      </c>
+      <c r="F11" s="26" t="str">
         <f>IF(C11="","",REPT("█",ROUND(C11*30,0)))</f>
-        <v/>
+        <v>█████████████████</v>
       </c>
       <c r="G11" s="21" t="n"/>
       <c r="H11" s="22" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="23">
+      <c r="A12" s="23" t="str">
         <f>IF(Metas!$A$17="","",Metas!$A$17)</f>
-        <v/>
+        <v>Organizar a casa</v>
       </c>
       <c r="B12" s="24">
         <f>IF(Metas!$A$17="","",COUNTIFS(Metas!$B$17:$B$20,"&lt;&gt;"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C12" s="25">
         <f>IF(OR(Metas!$A$17="",B12=0),"",AVERAGEIFS(Metas!$H$17:$H$20,Metas!$B$17:$B$20,"&lt;&gt;"))</f>
-        <v/>
+        <v>0.583333333333333</v>
       </c>
       <c r="D12" s="24">
         <f>IF(Metas!$A$17="","",COUNTIFS(Metas!$J$17:$J$20,"Atingido"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E12" s="24">
         <f>IF(Metas!$A$17="","",COUNTIFS(Metas!$J$17:$J$20,"Em risco"))</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
+        <v>1</v>
+      </c>
+      <c r="F12" s="26" t="str">
         <f>IF(C12="","",REPT("█",ROUND(C12*30,0)))</f>
-        <v/>
+        <v>█████████████████</v>
       </c>
       <c r="G12" s="21" t="n"/>
       <c r="H12" s="22" t="n"/>
@@ -1247,105 +1247,105 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23">
+      <c r="A17" s="23" t="str">
         <f>IF(Metas!B5="","",Metas!B5)</f>
-        <v/>
-      </c>
-      <c r="B17" s="24">
+        <v>Fechar 3 contratos mensais novos</v>
+      </c>
+      <c r="B17" s="24" t="str">
         <f>IF(Metas!B5="","",Metas!C5)</f>
-        <v/>
+        <v>Ana</v>
       </c>
       <c r="C17" s="27">
         <f>IF(Metas!B5="","",Metas!G5)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D17" s="27">
         <f>IF(Metas!B5="","",Metas!F5)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E17" s="25">
         <f>IF(Metas!B5="","",Metas!H5)</f>
-        <v/>
+        <v>0.666666666666667</v>
       </c>
       <c r="F17" s="25">
         <f>IF(Metas!B5="","",Metas!I5)</f>
-        <v/>
-      </c>
-      <c r="G17" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G17" s="24" t="str">
         <f>IF(Metas!B5="","",Metas!J5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="26">
+        <v>Atenção</v>
+      </c>
+      <c r="H17" s="26" t="str">
         <f>IF(E17="","",REPT("█",ROUND(E17*20,0)))</f>
-        <v/>
+        <v>█████████████</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23">
+      <c r="A18" s="23" t="str">
         <f>IF(Metas!B6="","",Metas!B6)</f>
-        <v/>
-      </c>
-      <c r="B18" s="24">
+        <v>Receita recorrente mensal de R$ 30 mil</v>
+      </c>
+      <c r="B18" s="24" t="str">
         <f>IF(Metas!B6="","",Metas!C6)</f>
-        <v/>
+        <v>Ana</v>
       </c>
       <c r="C18" s="27">
         <f>IF(Metas!B6="","",Metas!G6)</f>
-        <v/>
+        <v>27400</v>
       </c>
       <c r="D18" s="27">
         <f>IF(Metas!B6="","",Metas!F6)</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="E18" s="25">
         <f>IF(Metas!B6="","",Metas!H6)</f>
-        <v/>
+        <v>0.783333333333333</v>
       </c>
       <c r="F18" s="25">
         <f>IF(Metas!B6="","",Metas!I6)</f>
-        <v/>
-      </c>
-      <c r="G18" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G18" s="24" t="str">
         <f>IF(Metas!B6="","",Metas!J6)</f>
-        <v/>
-      </c>
-      <c r="H18" s="26">
+        <v>No ritmo</v>
+      </c>
+      <c r="H18" s="26" t="str">
         <f>IF(E18="","",REPT("█",ROUND(E18*20,0)))</f>
-        <v/>
+        <v>████████████████</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23">
+      <c r="A19" s="23" t="str">
         <f>IF(Metas!B7="","",Metas!B7)</f>
-        <v/>
-      </c>
-      <c r="B19" s="24">
+        <v>Propostas enviadas no trimestre</v>
+      </c>
+      <c r="B19" s="24" t="str">
         <f>IF(Metas!B7="","",Metas!C7)</f>
-        <v/>
+        <v>Carla</v>
       </c>
       <c r="C19" s="27">
         <f>IF(Metas!B7="","",Metas!G7)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="D19" s="27">
         <f>IF(Metas!B7="","",Metas!F7)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="E19" s="25">
         <f>IF(Metas!B7="","",Metas!H7)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F19" s="25">
         <f>IF(Metas!B7="","",Metas!I7)</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G19" s="24" t="str">
         <f>IF(Metas!B7="","",Metas!J7)</f>
-        <v/>
-      </c>
-      <c r="H19" s="26">
+        <v>Atingido</v>
+      </c>
+      <c r="H19" s="26" t="str">
         <f>IF(E19="","",REPT("█",ROUND(E19*20,0)))</f>
-        <v/>
+        <v>████████████████████</v>
       </c>
     </row>
     <row r="20">
@@ -1383,71 +1383,71 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23">
+      <c r="A21" s="23" t="str">
         <f>IF(Metas!B9="","",Metas!B9)</f>
-        <v/>
-      </c>
-      <c r="B21" s="24">
+        <v>Etapas atrasadas por semana (média)</v>
+      </c>
+      <c r="B21" s="24" t="str">
         <f>IF(Metas!B9="","",Metas!C9)</f>
-        <v/>
+        <v>Ana</v>
       </c>
       <c r="C21" s="27">
         <f>IF(Metas!B9="","",Metas!G9)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D21" s="27">
         <f>IF(Metas!B9="","",Metas!F9)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E21" s="25">
         <f>IF(Metas!B9="","",Metas!H9)</f>
-        <v/>
+        <v>0.333333333333333</v>
       </c>
       <c r="F21" s="25">
         <f>IF(Metas!B9="","",Metas!I9)</f>
-        <v/>
-      </c>
-      <c r="G21" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G21" s="24" t="str">
         <f>IF(Metas!B9="","",Metas!J9)</f>
-        <v/>
-      </c>
-      <c r="H21" s="26">
+        <v>Em risco</v>
+      </c>
+      <c r="H21" s="26" t="str">
         <f>IF(E21="","",REPT("█",ROUND(E21*20,0)))</f>
-        <v/>
+        <v>███████</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23">
+      <c r="A22" s="23" t="str">
         <f>IF(Metas!B10="","",Metas!B10)</f>
-        <v/>
-      </c>
-      <c r="B22" s="24">
+        <v>Projetos entregues na data combinada</v>
+      </c>
+      <c r="B22" s="24" t="str">
         <f>IF(Metas!B10="","",Metas!C10)</f>
-        <v/>
+        <v>Bruno</v>
       </c>
       <c r="C22" s="27">
         <f>IF(Metas!B10="","",Metas!G10)</f>
-        <v/>
+        <v>82</v>
       </c>
       <c r="D22" s="27">
         <f>IF(Metas!B10="","",Metas!F10)</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="E22" s="25">
         <f>IF(Metas!B10="","",Metas!H10)</f>
-        <v/>
+        <v>0.733333333333333</v>
       </c>
       <c r="F22" s="25">
         <f>IF(Metas!B10="","",Metas!I10)</f>
-        <v/>
-      </c>
-      <c r="G22" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G22" s="24" t="str">
         <f>IF(Metas!B10="","",Metas!J10)</f>
-        <v/>
-      </c>
-      <c r="H22" s="26">
+        <v>Atenção</v>
+      </c>
+      <c r="H22" s="26" t="str">
         <f>IF(E22="","",REPT("█",ROUND(E22*20,0)))</f>
-        <v/>
+        <v>███████████████</v>
       </c>
     </row>
     <row r="23">
@@ -1519,71 +1519,71 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23">
+      <c r="A25" s="23" t="str">
         <f>IF(Metas!B13="","",Metas!B13)</f>
-        <v/>
-      </c>
-      <c r="B25" s="24">
+        <v>Rodadas de revisão por peça (média)</v>
+      </c>
+      <c r="B25" s="24" t="str">
         <f>IF(Metas!B13="","",Metas!C13)</f>
-        <v/>
+        <v>Bruno</v>
       </c>
       <c r="C25" s="27">
         <f>IF(Metas!B13="","",Metas!G13)</f>
-        <v/>
+        <v>2.8</v>
       </c>
       <c r="D25" s="27">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E25" s="25">
         <f>IF(Metas!B13="","",Metas!H13)</f>
-        <v/>
+        <v>0.333333333333334</v>
       </c>
       <c r="F25" s="25">
         <f>IF(Metas!B13="","",Metas!I13)</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G25" s="24" t="str">
         <f>IF(Metas!B13="","",Metas!J13)</f>
-        <v/>
-      </c>
-      <c r="H25" s="26">
+        <v>Em risco</v>
+      </c>
+      <c r="H25" s="26" t="str">
         <f>IF(E25="","",REPT("█",ROUND(E25*20,0)))</f>
-        <v/>
+        <v>███████</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23">
+      <c r="A26" s="23" t="str">
         <f>IF(Metas!B14="","",Metas!B14)</f>
-        <v/>
-      </c>
-      <c r="B26" s="24">
+        <v>Peças aprovadas de primeira</v>
+      </c>
+      <c r="B26" s="24" t="str">
         <f>IF(Metas!B14="","",Metas!C14)</f>
-        <v/>
+        <v>Carla</v>
       </c>
       <c r="C26" s="27">
         <f>IF(Metas!B14="","",Metas!G14)</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="D26" s="27">
         <f>IF(Metas!B14="","",Metas!F14)</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="E26" s="25">
         <f>IF(Metas!B14="","",Metas!H14)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="F26" s="25">
         <f>IF(Metas!B14="","",Metas!I14)</f>
-        <v/>
-      </c>
-      <c r="G26" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G26" s="24" t="str">
         <f>IF(Metas!B14="","",Metas!J14)</f>
-        <v/>
-      </c>
-      <c r="H26" s="26">
+        <v>No ritmo</v>
+      </c>
+      <c r="H26" s="26" t="str">
         <f>IF(E26="","",REPT("█",ROUND(E26*20,0)))</f>
-        <v/>
+        <v>████████████████</v>
       </c>
     </row>
     <row r="27">
@@ -1655,71 +1655,71 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23">
+      <c r="A29" s="23" t="str">
         <f>IF(Metas!B17="","",Metas!B17)</f>
-        <v/>
-      </c>
-      <c r="B29" s="24">
+        <v>Relatório mensal enviado até o dia 5</v>
+      </c>
+      <c r="B29" s="24" t="str">
         <f>IF(Metas!B17="","",Metas!C17)</f>
-        <v/>
+        <v>Ana</v>
       </c>
       <c r="C29" s="27">
         <f>IF(Metas!B17="","",Metas!G17)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D29" s="27">
         <f>IF(Metas!B17="","",Metas!F17)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E29" s="25">
         <f>IF(Metas!B17="","",Metas!H17)</f>
-        <v/>
+        <v>0.666666666666667</v>
       </c>
       <c r="F29" s="25">
         <f>IF(Metas!B17="","",Metas!I17)</f>
-        <v/>
-      </c>
-      <c r="G29" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G29" s="24" t="str">
         <f>IF(Metas!B17="","",Metas!J17)</f>
-        <v/>
-      </c>
-      <c r="H29" s="26">
+        <v>Atenção</v>
+      </c>
+      <c r="H29" s="26" t="str">
         <f>IF(E29="","",REPT("█",ROUND(E29*20,0)))</f>
-        <v/>
+        <v>█████████████</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23">
+      <c r="A30" s="23" t="str">
         <f>IF(Metas!B18="","",Metas!B18)</f>
-        <v/>
-      </c>
-      <c r="B30" s="24">
+        <v>Horas extras da equipe no mês</v>
+      </c>
+      <c r="B30" s="24" t="str">
         <f>IF(Metas!B18="","",Metas!C18)</f>
-        <v/>
+        <v>Ana</v>
       </c>
       <c r="C30" s="27">
         <f>IF(Metas!B18="","",Metas!G18)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="D30" s="27">
         <f>IF(Metas!B18="","",Metas!F18)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E30" s="25">
         <f>IF(Metas!B18="","",Metas!H18)</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="F30" s="25">
         <f>IF(Metas!B18="","",Metas!I18)</f>
-        <v/>
-      </c>
-      <c r="G30" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="G30" s="24" t="str">
         <f>IF(Metas!B18="","",Metas!J18)</f>
-        <v/>
-      </c>
-      <c r="H30" s="26">
+        <v>Em risco</v>
+      </c>
+      <c r="H30" s="26" t="str">
         <f>IF(E30="","",REPT("█",ROUND(E30*20,0)))</f>
-        <v/>
+        <v>██████████</v>
       </c>
     </row>
     <row r="31">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B8" s="31">
         <f>TODAY()</f>
-        <v/>
+        <v>46282.0</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B9" s="24">
         <f>IF(B8&lt;B6,0,MIN(13,INT((B8-B6)/7)+1))</f>
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B10" s="25">
         <f>MAX(0,MIN(1,(B8-B6)/(B7-B6)))</f>
-        <v/>
+        <v>0.857142857142857</v>
       </c>
     </row>
   </sheetData>
@@ -2214,15 +2214,15 @@
       </c>
       <c r="H5" s="25">
         <f>IF(B5="","",IF(F5=E5,"",IF(K5="Menor é melhor",MAX(0,MIN(1,(E5-G5)/(E5-F5))),MAX(0,MIN(1,(G5-E5)/(F5-E5))))))</f>
-        <v/>
+        <v>0.666666666666667</v>
       </c>
       <c r="I5" s="25">
         <f>IF(B5="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J5" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J5" s="24" t="str">
         <f>IF(OR(B5="",H5=""),"",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Atenção</v>
       </c>
       <c r="K5" s="33" t="inlineStr">
         <is>
@@ -2259,15 +2259,15 @@
       </c>
       <c r="H6" s="25">
         <f>IF(B6="","",IF(F6=E6,"",IF(K6="Menor é melhor",MAX(0,MIN(1,(E6-G6)/(E6-F6))),MAX(0,MIN(1,(G6-E6)/(F6-E6))))))</f>
-        <v/>
+        <v>0.783333333333333</v>
       </c>
       <c r="I6" s="25">
         <f>IF(B6="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J6" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J6" s="24" t="str">
         <f>IF(OR(B6="",H6=""),"",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>No ritmo</v>
       </c>
       <c r="K6" s="33" t="inlineStr">
         <is>
@@ -2304,15 +2304,15 @@
       </c>
       <c r="H7" s="25">
         <f>IF(B7="","",IF(F7=E7,"",IF(K7="Menor é melhor",MAX(0,MIN(1,(E7-G7)/(E7-F7))),MAX(0,MIN(1,(G7-E7)/(F7-E7))))))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I7" s="25">
         <f>IF(B7="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J7" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J7" s="24" t="str">
         <f>IF(OR(B7="",H7=""),"",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Atingido</v>
       </c>
       <c r="K7" s="33" t="inlineStr">
         <is>
@@ -2376,15 +2376,15 @@
       </c>
       <c r="H9" s="25">
         <f>IF(B9="","",IF(F9=E9,"",IF(K9="Menor é melhor",MAX(0,MIN(1,(E9-G9)/(E9-F9))),MAX(0,MIN(1,(G9-E9)/(F9-E9))))))</f>
-        <v/>
+        <v>0.333333333333333</v>
       </c>
       <c r="I9" s="25">
         <f>IF(B9="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J9" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J9" s="24" t="str">
         <f>IF(OR(B9="",H9=""),"",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Em risco</v>
       </c>
       <c r="K9" s="33" t="inlineStr">
         <is>
@@ -2421,15 +2421,15 @@
       </c>
       <c r="H10" s="25">
         <f>IF(B10="","",IF(F10=E10,"",IF(K10="Menor é melhor",MAX(0,MIN(1,(E10-G10)/(E10-F10))),MAX(0,MIN(1,(G10-E10)/(F10-E10))))))</f>
-        <v/>
+        <v>0.733333333333333</v>
       </c>
       <c r="I10" s="25">
         <f>IF(B10="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J10" s="24" t="str">
         <f>IF(OR(B10="",H10=""),"",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Atenção</v>
       </c>
       <c r="K10" s="33" t="inlineStr">
         <is>
@@ -2516,15 +2516,15 @@
       </c>
       <c r="H13" s="25">
         <f>IF(B13="","",IF(F13=E13,"",IF(K13="Menor é melhor",MAX(0,MIN(1,(E13-G13)/(E13-F13))),MAX(0,MIN(1,(G13-E13)/(F13-E13))))))</f>
-        <v/>
+        <v>0.333333333333334</v>
       </c>
       <c r="I13" s="25">
         <f>IF(B13="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J13" s="24" t="str">
         <f>IF(OR(B13="",H13=""),"",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Em risco</v>
       </c>
       <c r="K13" s="33" t="inlineStr">
         <is>
@@ -2561,15 +2561,15 @@
       </c>
       <c r="H14" s="25">
         <f>IF(B14="","",IF(F14=E14,"",IF(K14="Menor é melhor",MAX(0,MIN(1,(E14-G14)/(E14-F14))),MAX(0,MIN(1,(G14-E14)/(F14-E14))))))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="I14" s="25">
         <f>IF(B14="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J14" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J14" s="24" t="str">
         <f>IF(OR(B14="",H14=""),"",IF(H14&gt;=1,"Atingido",IF(H14&gt;=I14-0.1,"No ritmo",IF(H14&gt;=I14-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>No ritmo</v>
       </c>
       <c r="K14" s="33" t="inlineStr">
         <is>
@@ -2656,15 +2656,15 @@
       </c>
       <c r="H17" s="25">
         <f>IF(B17="","",IF(F17=E17,"",IF(K17="Menor é melhor",MAX(0,MIN(1,(E17-G17)/(E17-F17))),MAX(0,MIN(1,(G17-E17)/(F17-E17))))))</f>
-        <v/>
+        <v>0.666666666666667</v>
       </c>
       <c r="I17" s="25">
         <f>IF(B17="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J17" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J17" s="24" t="str">
         <f>IF(OR(B17="",H17=""),"",IF(H17&gt;=1,"Atingido",IF(H17&gt;=I17-0.1,"No ritmo",IF(H17&gt;=I17-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Atenção</v>
       </c>
       <c r="K17" s="33" t="inlineStr">
         <is>
@@ -2701,15 +2701,15 @@
       </c>
       <c r="H18" s="25">
         <f>IF(B18="","",IF(F18=E18,"",IF(K18="Menor é melhor",MAX(0,MIN(1,(E18-G18)/(E18-F18))),MAX(0,MIN(1,(G18-E18)/(F18-E18))))))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="I18" s="25">
         <f>IF(B18="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J18" s="24">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="J18" s="24" t="str">
         <f>IF(OR(B18="",H18=""),"",IF(H18&gt;=1,"Atingido",IF(H18&gt;=I18-0.1,"No ritmo",IF(H18&gt;=I18-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Em risco</v>
       </c>
       <c r="K18" s="33" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23">
+      <c r="A5" s="23" t="str">
         <f>IF(Metas!B5="","",Metas!B5)</f>
-        <v/>
+        <v>Fechar 3 contratos mensais novos</v>
       </c>
       <c r="B5" s="24">
         <f>IF(Metas!B5="","",Metas!F5)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C5" s="33" t="n">
         <v>0</v>
@@ -3053,13 +3053,13 @@
       <c r="O5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="23">
+      <c r="A6" s="23" t="str">
         <f>IF(Metas!B6="","",Metas!B6)</f>
-        <v/>
+        <v>Receita recorrente mensal de R$ 30 mil</v>
       </c>
       <c r="B6" s="24">
         <f>IF(Metas!B6="","",Metas!F6)</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="C6" s="33" t="n">
         <v>18000</v>
@@ -3098,13 +3098,13 @@
       <c r="O6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="23">
+      <c r="A7" s="23" t="str">
         <f>IF(Metas!B7="","",Metas!B7)</f>
-        <v/>
+        <v>Propostas enviadas no trimestre</v>
       </c>
       <c r="B7" s="24">
         <f>IF(Metas!B7="","",Metas!F7)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="C7" s="33" t="n">
         <v>2</v>
@@ -3166,13 +3166,13 @@
       <c r="O8" s="33" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="23">
+      <c r="A9" s="23" t="str">
         <f>IF(Metas!B9="","",Metas!B9)</f>
-        <v/>
+        <v>Etapas atrasadas por semana (média)</v>
       </c>
       <c r="B9" s="24">
         <f>IF(Metas!B9="","",Metas!F9)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C9" s="33" t="n">
         <v>4</v>
@@ -3211,13 +3211,13 @@
       <c r="O9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="23">
+      <c r="A10" s="23" t="str">
         <f>IF(Metas!B10="","",Metas!B10)</f>
-        <v/>
+        <v>Projetos entregues na data combinada</v>
       </c>
       <c r="B10" s="24">
         <f>IF(Metas!B10="","",Metas!F10)</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="C10" s="33" t="n">
         <v>60</v>
@@ -3302,13 +3302,13 @@
       <c r="O12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="23">
+      <c r="A13" s="23" t="str">
         <f>IF(Metas!B13="","",Metas!B13)</f>
-        <v/>
+        <v>Rodadas de revisão por peça (média)</v>
       </c>
       <c r="B13" s="24">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C13" s="33" t="n">
         <v>3.2</v>
@@ -3347,13 +3347,13 @@
       <c r="O13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="23">
+      <c r="A14" s="23" t="str">
         <f>IF(Metas!B14="","",Metas!B14)</f>
-        <v/>
+        <v>Peças aprovadas de primeira</v>
       </c>
       <c r="B14" s="24">
         <f>IF(Metas!B14="","",Metas!F14)</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="C14" s="33" t="n">
         <v>40</v>
@@ -3438,13 +3438,13 @@
       <c r="O16" s="33" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="23">
+      <c r="A17" s="23" t="str">
         <f>IF(Metas!B17="","",Metas!B17)</f>
-        <v/>
+        <v>Relatório mensal enviado até o dia 5</v>
       </c>
       <c r="B17" s="24">
         <f>IF(Metas!B17="","",Metas!F17)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C17" s="33" t="n">
         <v>0</v>
@@ -3483,13 +3483,13 @@
       <c r="O17" s="33" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="23">
+      <c r="A18" s="23" t="str">
         <f>IF(Metas!B18="","",Metas!B18)</f>
-        <v/>
+        <v>Horas extras da equipe no mês</v>
       </c>
       <c r="B18" s="24">
         <f>IF(Metas!B18="","",Metas!F18)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C18" s="33" t="n">
         <v>20</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meses" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -843,7 +844,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Toda semana, atualize o valor atual e copie para a coluna da semana em Semanas. O Painel mostra o resumo por objetivo e a lista completa com semáforo.</t>
+          <t>Toda semana, atualize o valor atual e copie para a coluna da semana em Semanas. O Painel mostra o resumo por objetivo e a lista completa com semáforo; a aba Meses fecha cada mês do trimestre a partir das semanas, para a reunião mensal.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2885,7 @@
     <dataValidation sqref="K5:K24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Maior é melhor,Menor é melhor"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal"/>
+    <dataValidation sqref="E5:G24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3677,4 +3678,690 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Acompanhamento mensal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Fechamento de cada mês do trimestre: o último valor lançado nas semanas daquele mês. Nada para preencher aqui — vem da aba Semanas. Serve para a reunião do início do mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Resultado-chave</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Mês 3</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Ganho no trimestre</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Falta para a meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="str">
+        <f>IF(Metas!B5="","",Metas!B5)</f>
+        <v>Fechar 3 contratos mensais novos</v>
+      </c>
+      <c r="B5" s="24">
+        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <v>3</v>
+      </c>
+      <c r="C5" s="24">
+        <f>IF(Metas!B5="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C5:$F5),""))</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="24">
+        <f>IF(Metas!B5="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G5:$K5),""))</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="24">
+        <f>IF(Metas!B5="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L5:$O5),""))</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="24">
+        <f>IF(OR(Metas!B5="",C5="",E5=""),"",E5-IFERROR(Metas!E5,0))</f>
+        <v>2</v>
+      </c>
+      <c r="G5" s="24">
+        <f>IF(OR(Metas!B5="",E5=""),"",Metas!F5-E5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="str">
+        <f>IF(Metas!B6="","",Metas!B6)</f>
+        <v>Receita recorrente mensal de R$ 30 mil</v>
+      </c>
+      <c r="B6" s="24">
+        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <v>30000</v>
+      </c>
+      <c r="C6" s="24">
+        <f>IF(Metas!B6="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C6:$F6),""))</f>
+        <v>18000</v>
+      </c>
+      <c r="D6" s="24">
+        <f>IF(Metas!B6="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G6:$K6),""))</f>
+        <v>22500</v>
+      </c>
+      <c r="E6" s="24">
+        <f>IF(Metas!B6="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L6:$O6),""))</f>
+        <v>27400</v>
+      </c>
+      <c r="F6" s="24">
+        <f>IF(OR(Metas!B6="",C6="",E6=""),"",E6-IFERROR(Metas!E6,0))</f>
+        <v>9400</v>
+      </c>
+      <c r="G6" s="24">
+        <f>IF(OR(Metas!B6="",E6=""),"",Metas!F6-E6)</f>
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="str">
+        <f>IF(Metas!B7="","",Metas!B7)</f>
+        <v>Propostas enviadas no trimestre</v>
+      </c>
+      <c r="B7" s="24">
+        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <v>24</v>
+      </c>
+      <c r="C7" s="24">
+        <f>IF(Metas!B7="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C7:$F7),""))</f>
+        <v>9</v>
+      </c>
+      <c r="D7" s="24">
+        <f>IF(Metas!B7="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G7:$K7),""))</f>
+        <v>20</v>
+      </c>
+      <c r="E7" s="24">
+        <f>IF(Metas!B7="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L7:$O7),""))</f>
+        <v>24</v>
+      </c>
+      <c r="F7" s="24">
+        <f>IF(OR(Metas!B7="",C7="",E7=""),"",E7-IFERROR(Metas!E7,0))</f>
+        <v>24</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IF(OR(Metas!B7="",E7=""),"",Metas!F7-E7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23">
+        <f>IF(Metas!B8="","",Metas!B8)</f>
+        <v/>
+      </c>
+      <c r="B8" s="24">
+        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="24">
+        <f>IF(Metas!B8="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C8:$F8),""))</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>IF(Metas!B8="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G8:$K8),""))</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>IF(Metas!B8="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L8:$O8),""))</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
+        <f>IF(OR(Metas!B8="",C8="",E8=""),"",E8-IFERROR(Metas!E8,0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="24">
+        <f>IF(OR(Metas!B8="",E8=""),"",Metas!F8-E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="str">
+        <f>IF(Metas!B9="","",Metas!B9)</f>
+        <v>Etapas atrasadas por semana (média)</v>
+      </c>
+      <c r="B9" s="24">
+        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="24">
+        <f>IF(Metas!B9="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C9:$F9),""))</f>
+        <v>4</v>
+      </c>
+      <c r="D9" s="24">
+        <f>IF(Metas!B9="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G9:$K9),""))</f>
+        <v>4</v>
+      </c>
+      <c r="E9" s="24">
+        <f>IF(Metas!B9="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L9:$O9),""))</f>
+        <v>3</v>
+      </c>
+      <c r="F9" s="24">
+        <f>IF(OR(Metas!B9="",C9="",E9=""),"",E9-IFERROR(Metas!E9,0))</f>
+        <v>-1</v>
+      </c>
+      <c r="G9" s="24">
+        <f>IF(OR(Metas!B9="",E9=""),"",Metas!F9-E9)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="str">
+        <f>IF(Metas!B10="","",Metas!B10)</f>
+        <v>Projetos entregues na data combinada</v>
+      </c>
+      <c r="B10" s="24">
+        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <v>90</v>
+      </c>
+      <c r="C10" s="24">
+        <f>IF(Metas!B10="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C10:$F10),""))</f>
+        <v>67</v>
+      </c>
+      <c r="D10" s="24">
+        <f>IF(Metas!B10="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G10:$K10),""))</f>
+        <v>78</v>
+      </c>
+      <c r="E10" s="24">
+        <f>IF(Metas!B10="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L10:$O10),""))</f>
+        <v>82</v>
+      </c>
+      <c r="F10" s="24">
+        <f>IF(OR(Metas!B10="",C10="",E10=""),"",E10-IFERROR(Metas!E10,0))</f>
+        <v>22</v>
+      </c>
+      <c r="G10" s="24">
+        <f>IF(OR(Metas!B10="",E10=""),"",Metas!F10-E10)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23">
+        <f>IF(Metas!B11="","",Metas!B11)</f>
+        <v/>
+      </c>
+      <c r="B11" s="24">
+        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>IF(Metas!B11="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C11:$F11),""))</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>IF(Metas!B11="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G11:$K11),""))</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>IF(Metas!B11="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L11:$O11),""))</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>IF(OR(Metas!B11="",C11="",E11=""),"",E11-IFERROR(Metas!E11,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>IF(OR(Metas!B11="",E11=""),"",Metas!F11-E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23">
+        <f>IF(Metas!B12="","",Metas!B12)</f>
+        <v/>
+      </c>
+      <c r="B12" s="24">
+        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>IF(Metas!B12="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C12:$F12),""))</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>IF(Metas!B12="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G12:$K12),""))</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>IF(Metas!B12="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L12:$O12),""))</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>IF(OR(Metas!B12="",C12="",E12=""),"",E12-IFERROR(Metas!E12,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>IF(OR(Metas!B12="",E12=""),"",Metas!F12-E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="str">
+        <f>IF(Metas!B13="","",Metas!B13)</f>
+        <v>Rodadas de revisão por peça (média)</v>
+      </c>
+      <c r="B13" s="24">
+        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <v>2</v>
+      </c>
+      <c r="C13" s="24">
+        <f>IF(Metas!B13="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C13:$F13),""))</f>
+        <v>3</v>
+      </c>
+      <c r="D13" s="24">
+        <f>IF(Metas!B13="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G13:$K13),""))</f>
+        <v>2.8</v>
+      </c>
+      <c r="E13" s="24">
+        <f>IF(Metas!B13="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L13:$O13),""))</f>
+        <v>2.8</v>
+      </c>
+      <c r="F13" s="24">
+        <f>IF(OR(Metas!B13="",C13="",E13=""),"",E13-IFERROR(Metas!E13,0))</f>
+        <v>-0.4</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IF(OR(Metas!B13="",E13=""),"",Metas!F13-E13)</f>
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="str">
+        <f>IF(Metas!B14="","",Metas!B14)</f>
+        <v>Peças aprovadas de primeira</v>
+      </c>
+      <c r="B14" s="24">
+        <f>IF(Metas!B14="","",Metas!F14)</f>
+        <v>65</v>
+      </c>
+      <c r="C14" s="24">
+        <f>IF(Metas!B14="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C14:$F14),""))</f>
+        <v>48</v>
+      </c>
+      <c r="D14" s="24">
+        <f>IF(Metas!B14="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G14:$K14),""))</f>
+        <v>58</v>
+      </c>
+      <c r="E14" s="24">
+        <f>IF(Metas!B14="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L14:$O14),""))</f>
+        <v>60</v>
+      </c>
+      <c r="F14" s="24">
+        <f>IF(OR(Metas!B14="",C14="",E14=""),"",E14-IFERROR(Metas!E14,0))</f>
+        <v>20</v>
+      </c>
+      <c r="G14" s="24">
+        <f>IF(OR(Metas!B14="",E14=""),"",Metas!F14-E14)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23">
+        <f>IF(Metas!B15="","",Metas!B15)</f>
+        <v/>
+      </c>
+      <c r="B15" s="24">
+        <f>IF(Metas!B15="","",Metas!F15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
+        <f>IF(Metas!B15="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C15:$F15),""))</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>IF(Metas!B15="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G15:$K15),""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>IF(Metas!B15="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L15:$O15),""))</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>IF(OR(Metas!B15="",C15="",E15=""),"",E15-IFERROR(Metas!E15,0))</f>
+        <v/>
+      </c>
+      <c r="G15" s="24">
+        <f>IF(OR(Metas!B15="",E15=""),"",Metas!F15-E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23">
+        <f>IF(Metas!B16="","",Metas!B16)</f>
+        <v/>
+      </c>
+      <c r="B16" s="24">
+        <f>IF(Metas!B16="","",Metas!F16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>IF(Metas!B16="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C16:$F16),""))</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>IF(Metas!B16="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G16:$K16),""))</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>IF(Metas!B16="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L16:$O16),""))</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>IF(OR(Metas!B16="",C16="",E16=""),"",E16-IFERROR(Metas!E16,0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="24">
+        <f>IF(OR(Metas!B16="",E16=""),"",Metas!F16-E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="str">
+        <f>IF(Metas!B17="","",Metas!B17)</f>
+        <v>Relatório mensal enviado até o dia 5</v>
+      </c>
+      <c r="B17" s="24">
+        <f>IF(Metas!B17="","",Metas!F17)</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="24">
+        <f>IF(Metas!B17="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C17:$F17),""))</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="24">
+        <f>IF(Metas!B17="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G17:$K17),""))</f>
+        <v>1</v>
+      </c>
+      <c r="E17" s="24">
+        <f>IF(Metas!B17="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L17:$O17),""))</f>
+        <v>2</v>
+      </c>
+      <c r="F17" s="24">
+        <f>IF(OR(Metas!B17="",C17="",E17=""),"",E17-IFERROR(Metas!E17,0))</f>
+        <v>2</v>
+      </c>
+      <c r="G17" s="24">
+        <f>IF(OR(Metas!B17="",E17=""),"",Metas!F17-E17)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="str">
+        <f>IF(Metas!B18="","",Metas!B18)</f>
+        <v>Horas extras da equipe no mês</v>
+      </c>
+      <c r="B18" s="24">
+        <f>IF(Metas!B18="","",Metas!F18)</f>
+        <v>8</v>
+      </c>
+      <c r="C18" s="24">
+        <f>IF(Metas!B18="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C18:$F18),""))</f>
+        <v>18</v>
+      </c>
+      <c r="D18" s="24">
+        <f>IF(Metas!B18="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G18:$K18),""))</f>
+        <v>15</v>
+      </c>
+      <c r="E18" s="24">
+        <f>IF(Metas!B18="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L18:$O18),""))</f>
+        <v>14</v>
+      </c>
+      <c r="F18" s="24">
+        <f>IF(OR(Metas!B18="",C18="",E18=""),"",E18-IFERROR(Metas!E18,0))</f>
+        <v>-6</v>
+      </c>
+      <c r="G18" s="24">
+        <f>IF(OR(Metas!B18="",E18=""),"",Metas!F18-E18)</f>
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23">
+        <f>IF(Metas!B19="","",Metas!B19)</f>
+        <v/>
+      </c>
+      <c r="B19" s="24">
+        <f>IF(Metas!B19="","",Metas!F19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="24">
+        <f>IF(Metas!B19="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C19:$F19),""))</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>IF(Metas!B19="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G19:$K19),""))</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>IF(Metas!B19="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L19:$O19),""))</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
+        <f>IF(OR(Metas!B19="",C19="",E19=""),"",E19-IFERROR(Metas!E19,0))</f>
+        <v/>
+      </c>
+      <c r="G19" s="24">
+        <f>IF(OR(Metas!B19="",E19=""),"",Metas!F19-E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23">
+        <f>IF(Metas!B20="","",Metas!B20)</f>
+        <v/>
+      </c>
+      <c r="B20" s="24">
+        <f>IF(Metas!B20="","",Metas!F20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="24">
+        <f>IF(Metas!B20="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C20:$F20),""))</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>IF(Metas!B20="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G20:$K20),""))</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>IF(Metas!B20="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L20:$O20),""))</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>IF(OR(Metas!B20="",C20="",E20=""),"",E20-IFERROR(Metas!E20,0))</f>
+        <v/>
+      </c>
+      <c r="G20" s="24">
+        <f>IF(OR(Metas!B20="",E20=""),"",Metas!F20-E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23">
+        <f>IF(Metas!B21="","",Metas!B21)</f>
+        <v/>
+      </c>
+      <c r="B21" s="24">
+        <f>IF(Metas!B21="","",Metas!F21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="24">
+        <f>IF(Metas!B21="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C21:$F21),""))</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>IF(Metas!B21="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G21:$K21),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>IF(Metas!B21="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L21:$O21),""))</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>IF(OR(Metas!B21="",C21="",E21=""),"",E21-IFERROR(Metas!E21,0))</f>
+        <v/>
+      </c>
+      <c r="G21" s="24">
+        <f>IF(OR(Metas!B21="",E21=""),"",Metas!F21-E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23">
+        <f>IF(Metas!B22="","",Metas!B22)</f>
+        <v/>
+      </c>
+      <c r="B22" s="24">
+        <f>IF(Metas!B22="","",Metas!F22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="24">
+        <f>IF(Metas!B22="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C22:$F22),""))</f>
+        <v/>
+      </c>
+      <c r="D22" s="24">
+        <f>IF(Metas!B22="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G22:$K22),""))</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>IF(Metas!B22="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L22:$O22),""))</f>
+        <v/>
+      </c>
+      <c r="F22" s="24">
+        <f>IF(OR(Metas!B22="",C22="",E22=""),"",E22-IFERROR(Metas!E22,0))</f>
+        <v/>
+      </c>
+      <c r="G22" s="24">
+        <f>IF(OR(Metas!B22="",E22=""),"",Metas!F22-E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23">
+        <f>IF(Metas!B23="","",Metas!B23)</f>
+        <v/>
+      </c>
+      <c r="B23" s="24">
+        <f>IF(Metas!B23="","",Metas!F23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="24">
+        <f>IF(Metas!B23="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C23:$F23),""))</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>IF(Metas!B23="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G23:$K23),""))</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>IF(Metas!B23="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L23:$O23),""))</f>
+        <v/>
+      </c>
+      <c r="F23" s="24">
+        <f>IF(OR(Metas!B23="",C23="",E23=""),"",E23-IFERROR(Metas!E23,0))</f>
+        <v/>
+      </c>
+      <c r="G23" s="24">
+        <f>IF(OR(Metas!B23="",E23=""),"",Metas!F23-E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23">
+        <f>IF(Metas!B24="","",Metas!B24)</f>
+        <v/>
+      </c>
+      <c r="B24" s="24">
+        <f>IF(Metas!B24="","",Metas!F24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="24">
+        <f>IF(Metas!B24="","",IFERROR(LOOKUP(9.99E+307,Semanas!$C24:$F24),""))</f>
+        <v/>
+      </c>
+      <c r="D24" s="24">
+        <f>IF(Metas!B24="","",IFERROR(LOOKUP(9.99E+307,Semanas!$G24:$K24),""))</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>IF(Metas!B24="","",IFERROR(LOOKUP(9.99E+307,Semanas!$L24:$O24),""))</f>
+        <v/>
+      </c>
+      <c r="F24" s="24">
+        <f>IF(OR(Metas!B24="",C24="",E24=""),"",E24-IFERROR(Metas!E24,0))</f>
+        <v/>
+      </c>
+      <c r="G24" s="24">
+        <f>IF(OR(Metas!B24="",E24=""),"",Metas!F24-E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Mês 1 = semanas 1 a 4; Mês 2 = semanas 5 a 9; Mês 3 = semanas 10 a 13. Mês sem nenhuma semana preenchida fica em branco. "Ganho no trimestre" compara o fechamento do Mês 3 com o ponto de partida da aba Metas.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, preencha o trimestre, as datas de início e fim e deixe a data de referência em =HOJE().</t>
+          <t>Em Config, preencha o trimestre, as datas de início e fim e troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026, semana 11 de 13).</t>
         </is>
       </c>
     </row>
@@ -899,34 +899,58 @@
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -966,7 +990,7 @@
     <row r="2">
       <c r="A2" s="6" t="str">
         <f>"Semana "&amp;Config!B9&amp;" de 13 · "&amp;TEXT(Config!B10,"0%")&amp;" do trimestre decorrido. Nada para preencher aqui."</f>
-        <v>Semana 12 de 13 · 86% do trimestre decorrido. Nada para preencher aqui.</v>
+        <v>Semana 11 de 13 · 82% do trimestre decorrido. Nada para preencher aqui.</v>
       </c>
     </row>
     <row r="4">
@@ -1270,7 +1294,7 @@
       </c>
       <c r="F17" s="25">
         <f>IF(Metas!B5="","",Metas!I5)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G17" s="24" t="str">
         <f>IF(Metas!B5="","",Metas!J5)</f>
@@ -1304,7 +1328,7 @@
       </c>
       <c r="F18" s="25">
         <f>IF(Metas!B6="","",Metas!I6)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G18" s="24" t="str">
         <f>IF(Metas!B6="","",Metas!J6)</f>
@@ -1338,7 +1362,7 @@
       </c>
       <c r="F19" s="25">
         <f>IF(Metas!B7="","",Metas!I7)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G19" s="24" t="str">
         <f>IF(Metas!B7="","",Metas!J7)</f>
@@ -1406,7 +1430,7 @@
       </c>
       <c r="F21" s="25">
         <f>IF(Metas!B9="","",Metas!I9)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G21" s="24" t="str">
         <f>IF(Metas!B9="","",Metas!J9)</f>
@@ -1440,11 +1464,11 @@
       </c>
       <c r="F22" s="25">
         <f>IF(Metas!B10="","",Metas!I10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G22" s="24" t="str">
         <f>IF(Metas!B10="","",Metas!J10)</f>
-        <v>Atenção</v>
+        <v>No ritmo</v>
       </c>
       <c r="H22" s="26" t="str">
         <f>IF(E22="","",REPT("█",ROUND(E22*20,0)))</f>
@@ -1542,7 +1566,7 @@
       </c>
       <c r="F25" s="25">
         <f>IF(Metas!B13="","",Metas!I13)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G25" s="24" t="str">
         <f>IF(Metas!B13="","",Metas!J13)</f>
@@ -1576,7 +1600,7 @@
       </c>
       <c r="F26" s="25">
         <f>IF(Metas!B14="","",Metas!I14)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G26" s="24" t="str">
         <f>IF(Metas!B14="","",Metas!J14)</f>
@@ -1678,7 +1702,7 @@
       </c>
       <c r="F29" s="25">
         <f>IF(Metas!B17="","",Metas!I17)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G29" s="24" t="str">
         <f>IF(Metas!B17="","",Metas!J17)</f>
@@ -1712,7 +1736,7 @@
       </c>
       <c r="F30" s="25">
         <f>IF(Metas!B18="","",Metas!I18)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="G30" s="24" t="str">
         <f>IF(Metas!B18="","",Metas!J18)</f>
@@ -2043,13 +2067,12 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B8" s="31">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="B8" s="31" t="n">
+        <v>46279</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Para simular o fim do trimestre, troque por uma data.</t>
+          <t>O exemplo está congelado em 14/09/2026, para os arquivos do kit mostrarem a mesma foto. Ao usar com os seus dados, troque por =HOJE().</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2084,7 @@
       </c>
       <c r="B9" s="24">
         <f>IF(B8&lt;B6,0,MIN(13,INT((B8-B6)/7)+1))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2072,7 +2095,7 @@
       </c>
       <c r="B10" s="25">
         <f>MAX(0,MIN(1,(B8-B6)/(B7-B6)))</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
     </row>
   </sheetData>
@@ -2219,7 +2242,7 @@
       </c>
       <c r="I5" s="25">
         <f>IF(B5="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J5" s="24" t="str">
         <f>IF(OR(B5="",H5=""),"",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco"))))</f>
@@ -2264,7 +2287,7 @@
       </c>
       <c r="I6" s="25">
         <f>IF(B6="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J6" s="24" t="str">
         <f>IF(OR(B6="",H6=""),"",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco"))))</f>
@@ -2309,7 +2332,7 @@
       </c>
       <c r="I7" s="25">
         <f>IF(B7="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J7" s="24" t="str">
         <f>IF(OR(B7="",H7=""),"",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco"))))</f>
@@ -2381,7 +2404,7 @@
       </c>
       <c r="I9" s="25">
         <f>IF(B9="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J9" s="24" t="str">
         <f>IF(OR(B9="",H9=""),"",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco"))))</f>
@@ -2426,11 +2449,11 @@
       </c>
       <c r="I10" s="25">
         <f>IF(B10="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J10" s="24" t="str">
         <f>IF(OR(B10="",H10=""),"",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco"))))</f>
-        <v>Atenção</v>
+        <v>No ritmo</v>
       </c>
       <c r="K10" s="33" t="inlineStr">
         <is>
@@ -2521,7 +2544,7 @@
       </c>
       <c r="I13" s="25">
         <f>IF(B13="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J13" s="24" t="str">
         <f>IF(OR(B13="",H13=""),"",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco"))))</f>
@@ -2566,7 +2589,7 @@
       </c>
       <c r="I14" s="25">
         <f>IF(B14="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J14" s="24" t="str">
         <f>IF(OR(B14="",H14=""),"",IF(H14&gt;=1,"Atingido",IF(H14&gt;=I14-0.1,"No ritmo",IF(H14&gt;=I14-0.25,"Atenção","Em risco"))))</f>
@@ -2661,7 +2684,7 @@
       </c>
       <c r="I17" s="25">
         <f>IF(B17="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J17" s="24" t="str">
         <f>IF(OR(B17="",H17=""),"",IF(H17&gt;=1,"Atingido",IF(H17&gt;=I17-0.1,"No ritmo",IF(H17&gt;=I17-0.25,"Atenção","Em risco"))))</f>
@@ -2706,7 +2729,7 @@
       </c>
       <c r="I18" s="25">
         <f>IF(B18="","",Config!$B$10)</f>
-        <v>0.857142857142857</v>
+        <v>0.824175824175824</v>
       </c>
       <c r="J18" s="24" t="str">
         <f>IF(OR(B18="",H18=""),"",IF(H18&gt;=1,"Atingido",IF(H18&gt;=I18-0.1,"No ritmo",IF(H18&gt;=I18-0.25,"Atenção","Em risco"))))</f>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
   </mergeCells>
   <conditionalFormatting sqref="C4:O4">
     <cfRule type="expression" priority="1" dxfId="4">
-      <formula>COLUMN()-2=Config!$B$9</formula>
+      <formula>COLUMN()-2=INDIRECT("Config!$B$9")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3794,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="24">
-        <f>IF(OR(Metas!B5="",C5="",E5=""),"",E5-IFERROR(Metas!E5,0))</f>
+        <f>IF(OR(Metas!B5="",E5=""),"",E5-IFERROR(Metas!E5,0))</f>
         <v>2</v>
       </c>
       <c r="G5" s="24">
@@ -3824,7 +3824,7 @@
         <v>27400</v>
       </c>
       <c r="F6" s="24">
-        <f>IF(OR(Metas!B6="",C6="",E6=""),"",E6-IFERROR(Metas!E6,0))</f>
+        <f>IF(OR(Metas!B6="",E6=""),"",E6-IFERROR(Metas!E6,0))</f>
         <v>9400</v>
       </c>
       <c r="G6" s="24">
@@ -3854,7 +3854,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="24">
-        <f>IF(OR(Metas!B7="",C7="",E7=""),"",E7-IFERROR(Metas!E7,0))</f>
+        <f>IF(OR(Metas!B7="",E7=""),"",E7-IFERROR(Metas!E7,0))</f>
         <v>24</v>
       </c>
       <c r="G7" s="24">
@@ -3884,7 +3884,7 @@
         <v/>
       </c>
       <c r="F8" s="24">
-        <f>IF(OR(Metas!B8="",C8="",E8=""),"",E8-IFERROR(Metas!E8,0))</f>
+        <f>IF(OR(Metas!B8="",E8=""),"",E8-IFERROR(Metas!E8,0))</f>
         <v/>
       </c>
       <c r="G8" s="24">
@@ -3914,7 +3914,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="24">
-        <f>IF(OR(Metas!B9="",C9="",E9=""),"",E9-IFERROR(Metas!E9,0))</f>
+        <f>IF(OR(Metas!B9="",E9=""),"",E9-IFERROR(Metas!E9,0))</f>
         <v>-1</v>
       </c>
       <c r="G9" s="24">
@@ -3944,7 +3944,7 @@
         <v>82</v>
       </c>
       <c r="F10" s="24">
-        <f>IF(OR(Metas!B10="",C10="",E10=""),"",E10-IFERROR(Metas!E10,0))</f>
+        <f>IF(OR(Metas!B10="",E10=""),"",E10-IFERROR(Metas!E10,0))</f>
         <v>22</v>
       </c>
       <c r="G10" s="24">
@@ -3974,7 +3974,7 @@
         <v/>
       </c>
       <c r="F11" s="24">
-        <f>IF(OR(Metas!B11="",C11="",E11=""),"",E11-IFERROR(Metas!E11,0))</f>
+        <f>IF(OR(Metas!B11="",E11=""),"",E11-IFERROR(Metas!E11,0))</f>
         <v/>
       </c>
       <c r="G11" s="24">
@@ -4004,7 +4004,7 @@
         <v/>
       </c>
       <c r="F12" s="24">
-        <f>IF(OR(Metas!B12="",C12="",E12=""),"",E12-IFERROR(Metas!E12,0))</f>
+        <f>IF(OR(Metas!B12="",E12=""),"",E12-IFERROR(Metas!E12,0))</f>
         <v/>
       </c>
       <c r="G12" s="24">
@@ -4034,7 +4034,7 @@
         <v>2.8</v>
       </c>
       <c r="F13" s="24">
-        <f>IF(OR(Metas!B13="",C13="",E13=""),"",E13-IFERROR(Metas!E13,0))</f>
+        <f>IF(OR(Metas!B13="",E13=""),"",E13-IFERROR(Metas!E13,0))</f>
         <v>-0.4</v>
       </c>
       <c r="G13" s="24">
@@ -4064,7 +4064,7 @@
         <v>60</v>
       </c>
       <c r="F14" s="24">
-        <f>IF(OR(Metas!B14="",C14="",E14=""),"",E14-IFERROR(Metas!E14,0))</f>
+        <f>IF(OR(Metas!B14="",E14=""),"",E14-IFERROR(Metas!E14,0))</f>
         <v>20</v>
       </c>
       <c r="G14" s="24">
@@ -4094,7 +4094,7 @@
         <v/>
       </c>
       <c r="F15" s="24">
-        <f>IF(OR(Metas!B15="",C15="",E15=""),"",E15-IFERROR(Metas!E15,0))</f>
+        <f>IF(OR(Metas!B15="",E15=""),"",E15-IFERROR(Metas!E15,0))</f>
         <v/>
       </c>
       <c r="G15" s="24">
@@ -4124,7 +4124,7 @@
         <v/>
       </c>
       <c r="F16" s="24">
-        <f>IF(OR(Metas!B16="",C16="",E16=""),"",E16-IFERROR(Metas!E16,0))</f>
+        <f>IF(OR(Metas!B16="",E16=""),"",E16-IFERROR(Metas!E16,0))</f>
         <v/>
       </c>
       <c r="G16" s="24">
@@ -4154,7 +4154,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="24">
-        <f>IF(OR(Metas!B17="",C17="",E17=""),"",E17-IFERROR(Metas!E17,0))</f>
+        <f>IF(OR(Metas!B17="",E17=""),"",E17-IFERROR(Metas!E17,0))</f>
         <v>2</v>
       </c>
       <c r="G17" s="24">
@@ -4184,7 +4184,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="24">
-        <f>IF(OR(Metas!B18="",C18="",E18=""),"",E18-IFERROR(Metas!E18,0))</f>
+        <f>IF(OR(Metas!B18="",E18=""),"",E18-IFERROR(Metas!E18,0))</f>
         <v>-6</v>
       </c>
       <c r="G18" s="24">
@@ -4214,7 +4214,7 @@
         <v/>
       </c>
       <c r="F19" s="24">
-        <f>IF(OR(Metas!B19="",C19="",E19=""),"",E19-IFERROR(Metas!E19,0))</f>
+        <f>IF(OR(Metas!B19="",E19=""),"",E19-IFERROR(Metas!E19,0))</f>
         <v/>
       </c>
       <c r="G19" s="24">
@@ -4244,7 +4244,7 @@
         <v/>
       </c>
       <c r="F20" s="24">
-        <f>IF(OR(Metas!B20="",C20="",E20=""),"",E20-IFERROR(Metas!E20,0))</f>
+        <f>IF(OR(Metas!B20="",E20=""),"",E20-IFERROR(Metas!E20,0))</f>
         <v/>
       </c>
       <c r="G20" s="24">
@@ -4274,7 +4274,7 @@
         <v/>
       </c>
       <c r="F21" s="24">
-        <f>IF(OR(Metas!B21="",C21="",E21=""),"",E21-IFERROR(Metas!E21,0))</f>
+        <f>IF(OR(Metas!B21="",E21=""),"",E21-IFERROR(Metas!E21,0))</f>
         <v/>
       </c>
       <c r="G21" s="24">
@@ -4304,7 +4304,7 @@
         <v/>
       </c>
       <c r="F22" s="24">
-        <f>IF(OR(Metas!B22="",C22="",E22=""),"",E22-IFERROR(Metas!E22,0))</f>
+        <f>IF(OR(Metas!B22="",E22=""),"",E22-IFERROR(Metas!E22,0))</f>
         <v/>
       </c>
       <c r="G22" s="24">
@@ -4334,7 +4334,7 @@
         <v/>
       </c>
       <c r="F23" s="24">
-        <f>IF(OR(Metas!B23="",C23="",E23=""),"",E23-IFERROR(Metas!E23,0))</f>
+        <f>IF(OR(Metas!B23="",E23=""),"",E23-IFERROR(Metas!E23,0))</f>
         <v/>
       </c>
       <c r="G23" s="24">
@@ -4364,7 +4364,7 @@
         <v/>
       </c>
       <c r="F24" s="24">
-        <f>IF(OR(Metas!B24="",C24="",E24=""),"",E24-IFERROR(Metas!E24,0))</f>
+        <f>IF(OR(Metas!B24="",E24=""),"",E24-IFERROR(Metas!E24,0))</f>
         <v/>
       </c>
       <c r="G24" s="24">

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -2113,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2237,7 +2237,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(B5="","",IF(F5=E5,"",IF(K5="Menor é melhor",MAX(0,MIN(1,(E5-G5)/(E5-F5))),MAX(0,MIN(1,(G5-E5)/(F5-E5))))))</f>
+        <f>IF(OR(B5="",G5=""),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),IF(G5=0,0,MAX(0,F5/G5)))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),IF(F5=0,0,MAX(0,G5/F5))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I5" s="25">
@@ -2282,7 +2282,7 @@
         <v>27400</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(B6="","",IF(F6=E6,"",IF(K6="Menor é melhor",MAX(0,MIN(1,(E6-G6)/(E6-F6))),MAX(0,MIN(1,(G6-E6)/(F6-E6))))))</f>
+        <f>IF(OR(B6="",G6=""),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),IF(G6=0,0,MAX(0,F6/G6)))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),IF(F6=0,0,MAX(0,G6/F6))))))</f>
         <v>0.783333333333333</v>
       </c>
       <c r="I6" s="25">
@@ -2327,7 +2327,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(B7="","",IF(F7=E7,"",IF(K7="Menor é melhor",MAX(0,MIN(1,(E7-G7)/(E7-F7))),MAX(0,MIN(1,(G7-E7)/(F7-E7))))))</f>
+        <f>IF(OR(B7="",G7=""),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),IF(G7=0,0,MAX(0,F7/G7)))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),IF(F7=0,0,MAX(0,G7/F7))))))</f>
         <v>1</v>
       </c>
       <c r="I7" s="25">
@@ -2354,7 +2354,7 @@
       <c r="F8" s="33" t="n"/>
       <c r="G8" s="33" t="n"/>
       <c r="H8" s="25">
-        <f>IF(B8="","",IF(F8=E8,"",IF(K8="Menor é melhor",MAX(0,MIN(1,(E8-G8)/(E8-F8))),MAX(0,MIN(1,(G8-E8)/(F8-E8))))))</f>
+        <f>IF(OR(B8="",G8=""),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),IF(G8=0,0,MAX(0,F8/G8)))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),IF(F8=0,0,MAX(0,G8/F8))))))</f>
         <v/>
       </c>
       <c r="I8" s="25">
@@ -2399,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(B9="","",IF(F9=E9,"",IF(K9="Menor é melhor",MAX(0,MIN(1,(E9-G9)/(E9-F9))),MAX(0,MIN(1,(G9-E9)/(F9-E9))))))</f>
+        <f>IF(OR(B9="",G9=""),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),IF(G9=0,0,MAX(0,F9/G9)))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),IF(F9=0,0,MAX(0,G9/F9))))))</f>
         <v>0.333333333333333</v>
       </c>
       <c r="I9" s="25">
@@ -2444,7 +2444,7 @@
         <v>82</v>
       </c>
       <c r="H10" s="25">
-        <f>IF(B10="","",IF(F10=E10,"",IF(K10="Menor é melhor",MAX(0,MIN(1,(E10-G10)/(E10-F10))),MAX(0,MIN(1,(G10-E10)/(F10-E10))))))</f>
+        <f>IF(OR(B10="",G10=""),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),IF(G10=0,0,MAX(0,F10/G10)))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),IF(F10=0,0,MAX(0,G10/F10))))))</f>
         <v>0.733333333333333</v>
       </c>
       <c r="I10" s="25">
@@ -2471,7 +2471,7 @@
       <c r="F11" s="33" t="n"/>
       <c r="G11" s="33" t="n"/>
       <c r="H11" s="25">
-        <f>IF(B11="","",IF(F11=E11,"",IF(K11="Menor é melhor",MAX(0,MIN(1,(E11-G11)/(E11-F11))),MAX(0,MIN(1,(G11-E11)/(F11-E11))))))</f>
+        <f>IF(OR(B11="",G11=""),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),IF(G11=0,0,MAX(0,F11/G11)))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),IF(F11=0,0,MAX(0,G11/F11))))))</f>
         <v/>
       </c>
       <c r="I11" s="25">
@@ -2494,7 +2494,7 @@
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="33" t="n"/>
       <c r="H12" s="25">
-        <f>IF(B12="","",IF(F12=E12,"",IF(K12="Menor é melhor",MAX(0,MIN(1,(E12-G12)/(E12-F12))),MAX(0,MIN(1,(G12-E12)/(F12-E12))))))</f>
+        <f>IF(OR(B12="",G12=""),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),IF(G12=0,0,MAX(0,F12/G12)))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),IF(F12=0,0,MAX(0,G12/F12))))))</f>
         <v/>
       </c>
       <c r="I12" s="25">
@@ -2539,7 +2539,7 @@
         <v>2.8</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(B13="","",IF(F13=E13,"",IF(K13="Menor é melhor",MAX(0,MIN(1,(E13-G13)/(E13-F13))),MAX(0,MIN(1,(G13-E13)/(F13-E13))))))</f>
+        <f>IF(OR(B13="",G13=""),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),IF(G13=0,0,MAX(0,F13/G13)))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),IF(F13=0,0,MAX(0,G13/F13))))))</f>
         <v>0.333333333333334</v>
       </c>
       <c r="I13" s="25">
@@ -2584,7 +2584,7 @@
         <v>60</v>
       </c>
       <c r="H14" s="25">
-        <f>IF(B14="","",IF(F14=E14,"",IF(K14="Menor é melhor",MAX(0,MIN(1,(E14-G14)/(E14-F14))),MAX(0,MIN(1,(G14-E14)/(F14-E14))))))</f>
+        <f>IF(OR(B14="",G14=""),"",IF(K14="Menor é melhor",IF(G14&lt;=F14,1,IF(E14&gt;F14,MAX(0,(E14-G14)/(E14-F14)),IF(G14=0,0,MAX(0,F14/G14)))),IF(G14&gt;=F14,1,IF(E14&lt;F14,MAX(0,(G14-E14)/(F14-E14)),IF(F14=0,0,MAX(0,G14/F14))))))</f>
         <v>0.8</v>
       </c>
       <c r="I14" s="25">
@@ -2611,7 +2611,7 @@
       <c r="F15" s="33" t="n"/>
       <c r="G15" s="33" t="n"/>
       <c r="H15" s="25">
-        <f>IF(B15="","",IF(F15=E15,"",IF(K15="Menor é melhor",MAX(0,MIN(1,(E15-G15)/(E15-F15))),MAX(0,MIN(1,(G15-E15)/(F15-E15))))))</f>
+        <f>IF(OR(B15="",G15=""),"",IF(K15="Menor é melhor",IF(G15&lt;=F15,1,IF(E15&gt;F15,MAX(0,(E15-G15)/(E15-F15)),IF(G15=0,0,MAX(0,F15/G15)))),IF(G15&gt;=F15,1,IF(E15&lt;F15,MAX(0,(G15-E15)/(F15-E15)),IF(F15=0,0,MAX(0,G15/F15))))))</f>
         <v/>
       </c>
       <c r="I15" s="25">
@@ -2634,7 +2634,7 @@
       <c r="F16" s="33" t="n"/>
       <c r="G16" s="33" t="n"/>
       <c r="H16" s="25">
-        <f>IF(B16="","",IF(F16=E16,"",IF(K16="Menor é melhor",MAX(0,MIN(1,(E16-G16)/(E16-F16))),MAX(0,MIN(1,(G16-E16)/(F16-E16))))))</f>
+        <f>IF(OR(B16="",G16=""),"",IF(K16="Menor é melhor",IF(G16&lt;=F16,1,IF(E16&gt;F16,MAX(0,(E16-G16)/(E16-F16)),IF(G16=0,0,MAX(0,F16/G16)))),IF(G16&gt;=F16,1,IF(E16&lt;F16,MAX(0,(G16-E16)/(F16-E16)),IF(F16=0,0,MAX(0,G16/F16))))))</f>
         <v/>
       </c>
       <c r="I16" s="25">
@@ -2679,7 +2679,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="25">
-        <f>IF(B17="","",IF(F17=E17,"",IF(K17="Menor é melhor",MAX(0,MIN(1,(E17-G17)/(E17-F17))),MAX(0,MIN(1,(G17-E17)/(F17-E17))))))</f>
+        <f>IF(OR(B17="",G17=""),"",IF(K17="Menor é melhor",IF(G17&lt;=F17,1,IF(E17&gt;F17,MAX(0,(E17-G17)/(E17-F17)),IF(G17=0,0,MAX(0,F17/G17)))),IF(G17&gt;=F17,1,IF(E17&lt;F17,MAX(0,(G17-E17)/(F17-E17)),IF(F17=0,0,MAX(0,G17/F17))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I17" s="25">
@@ -2724,7 +2724,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="25">
-        <f>IF(B18="","",IF(F18=E18,"",IF(K18="Menor é melhor",MAX(0,MIN(1,(E18-G18)/(E18-F18))),MAX(0,MIN(1,(G18-E18)/(F18-E18))))))</f>
+        <f>IF(OR(B18="",G18=""),"",IF(K18="Menor é melhor",IF(G18&lt;=F18,1,IF(E18&gt;F18,MAX(0,(E18-G18)/(E18-F18)),IF(G18=0,0,MAX(0,F18/G18)))),IF(G18&gt;=F18,1,IF(E18&lt;F18,MAX(0,(G18-E18)/(F18-E18)),IF(F18=0,0,MAX(0,G18/F18))))))</f>
         <v>0.5</v>
       </c>
       <c r="I18" s="25">
@@ -2751,7 +2751,7 @@
       <c r="F19" s="33" t="n"/>
       <c r="G19" s="33" t="n"/>
       <c r="H19" s="25">
-        <f>IF(B19="","",IF(F19=E19,"",IF(K19="Menor é melhor",MAX(0,MIN(1,(E19-G19)/(E19-F19))),MAX(0,MIN(1,(G19-E19)/(F19-E19))))))</f>
+        <f>IF(OR(B19="",G19=""),"",IF(K19="Menor é melhor",IF(G19&lt;=F19,1,IF(E19&gt;F19,MAX(0,(E19-G19)/(E19-F19)),IF(G19=0,0,MAX(0,F19/G19)))),IF(G19&gt;=F19,1,IF(E19&lt;F19,MAX(0,(G19-E19)/(F19-E19)),IF(F19=0,0,MAX(0,G19/F19))))))</f>
         <v/>
       </c>
       <c r="I19" s="25">
@@ -2774,7 +2774,7 @@
       <c r="F20" s="33" t="n"/>
       <c r="G20" s="33" t="n"/>
       <c r="H20" s="25">
-        <f>IF(B20="","",IF(F20=E20,"",IF(K20="Menor é melhor",MAX(0,MIN(1,(E20-G20)/(E20-F20))),MAX(0,MIN(1,(G20-E20)/(F20-E20))))))</f>
+        <f>IF(OR(B20="",G20=""),"",IF(K20="Menor é melhor",IF(G20&lt;=F20,1,IF(E20&gt;F20,MAX(0,(E20-G20)/(E20-F20)),IF(G20=0,0,MAX(0,F20/G20)))),IF(G20&gt;=F20,1,IF(E20&lt;F20,MAX(0,(G20-E20)/(F20-E20)),IF(F20=0,0,MAX(0,G20/F20))))))</f>
         <v/>
       </c>
       <c r="I20" s="25">
@@ -2797,7 +2797,7 @@
       <c r="F21" s="33" t="n"/>
       <c r="G21" s="33" t="n"/>
       <c r="H21" s="25">
-        <f>IF(B21="","",IF(F21=E21,"",IF(K21="Menor é melhor",MAX(0,MIN(1,(E21-G21)/(E21-F21))),MAX(0,MIN(1,(G21-E21)/(F21-E21))))))</f>
+        <f>IF(OR(B21="",G21=""),"",IF(K21="Menor é melhor",IF(G21&lt;=F21,1,IF(E21&gt;F21,MAX(0,(E21-G21)/(E21-F21)),IF(G21=0,0,MAX(0,F21/G21)))),IF(G21&gt;=F21,1,IF(E21&lt;F21,MAX(0,(G21-E21)/(F21-E21)),IF(F21=0,0,MAX(0,G21/F21))))))</f>
         <v/>
       </c>
       <c r="I21" s="25">
@@ -2820,7 +2820,7 @@
       <c r="F22" s="33" t="n"/>
       <c r="G22" s="33" t="n"/>
       <c r="H22" s="25">
-        <f>IF(B22="","",IF(F22=E22,"",IF(K22="Menor é melhor",MAX(0,MIN(1,(E22-G22)/(E22-F22))),MAX(0,MIN(1,(G22-E22)/(F22-E22))))))</f>
+        <f>IF(OR(B22="",G22=""),"",IF(K22="Menor é melhor",IF(G22&lt;=F22,1,IF(E22&gt;F22,MAX(0,(E22-G22)/(E22-F22)),IF(G22=0,0,MAX(0,F22/G22)))),IF(G22&gt;=F22,1,IF(E22&lt;F22,MAX(0,(G22-E22)/(F22-E22)),IF(F22=0,0,MAX(0,G22/F22))))))</f>
         <v/>
       </c>
       <c r="I22" s="25">
@@ -2843,7 +2843,7 @@
       <c r="F23" s="33" t="n"/>
       <c r="G23" s="33" t="n"/>
       <c r="H23" s="25">
-        <f>IF(B23="","",IF(F23=E23,"",IF(K23="Menor é melhor",MAX(0,MIN(1,(E23-G23)/(E23-F23))),MAX(0,MIN(1,(G23-E23)/(F23-E23))))))</f>
+        <f>IF(OR(B23="",G23=""),"",IF(K23="Menor é melhor",IF(G23&lt;=F23,1,IF(E23&gt;F23,MAX(0,(E23-G23)/(E23-F23)),IF(G23=0,0,MAX(0,F23/G23)))),IF(G23&gt;=F23,1,IF(E23&lt;F23,MAX(0,(G23-E23)/(F23-E23)),IF(F23=0,0,MAX(0,G23/F23))))))</f>
         <v/>
       </c>
       <c r="I23" s="25">
@@ -2866,7 +2866,7 @@
       <c r="F24" s="33" t="n"/>
       <c r="G24" s="33" t="n"/>
       <c r="H24" s="25">
-        <f>IF(B24="","",IF(F24=E24,"",IF(K24="Menor é melhor",MAX(0,MIN(1,(E24-G24)/(E24-F24))),MAX(0,MIN(1,(G24-E24)/(F24-E24))))))</f>
+        <f>IF(OR(B24="",G24=""),"",IF(K24="Menor é melhor",IF(G24&lt;=F24,1,IF(E24&gt;F24,MAX(0,(E24-G24)/(E24-F24)),IF(G24=0,0,MAX(0,F24/G24)))),IF(G24&gt;=F24,1,IF(E24&lt;F24,MAX(0,(G24-E24)/(F24-E24)),IF(F24=0,0,MAX(0,G24/F24))))))</f>
         <v/>
       </c>
       <c r="I24" s="25">
@@ -2879,6 +2879,13 @@
       </c>
       <c r="K24" s="33" t="n"/>
       <c r="L24" s="34" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Progresso: valor atual no alvo = 100 %; fora do alvo, é o caminho andado entre o ponto de partida e a meta — e, quando o ponto de partida já estava dentro da meta (um teto ou piso a manter), é meta ÷ atual (16 horas extras para um teto de 8 = 50 %). Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -353,7 +353,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="008A86A0"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1973,15 +1985,18 @@
   </mergeCells>
   <conditionalFormatting sqref="G17:G36">
     <cfRule type="expression" priority="1" dxfId="0">
+      <formula>G17="Faltam dados"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>G17="Atingido"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>G17="No ritmo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="3">
       <formula>G17="Atenção"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>G17="Em risco"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2237,7 +2252,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(OR(B5="",G5=""),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),IF(G5=0,0,MAX(0,F5/G5)))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),IF(F5=0,0,MAX(0,G5/F5))))))</f>
+        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I5" s="25">
@@ -2245,7 +2260,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J5" s="24" t="str">
-        <f>IF(OR(B5="",H5=""),"",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B5="","",IF(H5="","Faltam dados",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco")))))</f>
         <v>Atenção</v>
       </c>
       <c r="K5" s="33" t="inlineStr">
@@ -2282,7 +2297,7 @@
         <v>27400</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(OR(B6="",G6=""),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),IF(G6=0,0,MAX(0,F6/G6)))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),IF(F6=0,0,MAX(0,G6/F6))))))</f>
+        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
         <v>0.783333333333333</v>
       </c>
       <c r="I6" s="25">
@@ -2290,7 +2305,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J6" s="24" t="str">
-        <f>IF(OR(B6="",H6=""),"",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B6="","",IF(H6="","Faltam dados",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K6" s="33" t="inlineStr">
@@ -2327,7 +2342,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(OR(B7="",G7=""),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),IF(G7=0,0,MAX(0,F7/G7)))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),IF(F7=0,0,MAX(0,G7/F7))))))</f>
+        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
         <v>1</v>
       </c>
       <c r="I7" s="25">
@@ -2335,7 +2350,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J7" s="24" t="str">
-        <f>IF(OR(B7="",H7=""),"",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B7="","",IF(H7="","Faltam dados",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco")))))</f>
         <v>Atingido</v>
       </c>
       <c r="K7" s="33" t="inlineStr">
@@ -2354,7 +2369,7 @@
       <c r="F8" s="33" t="n"/>
       <c r="G8" s="33" t="n"/>
       <c r="H8" s="25">
-        <f>IF(OR(B8="",G8=""),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),IF(G8=0,0,MAX(0,F8/G8)))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),IF(F8=0,0,MAX(0,G8/F8))))))</f>
+        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
         <v/>
       </c>
       <c r="I8" s="25">
@@ -2362,7 +2377,7 @@
         <v/>
       </c>
       <c r="J8" s="24">
-        <f>IF(OR(B8="",H8=""),"",IF(H8&gt;=1,"Atingido",IF(H8&gt;=I8-0.1,"No ritmo",IF(H8&gt;=I8-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B8="","",IF(H8="","Faltam dados",IF(H8&gt;=1,"Atingido",IF(H8&gt;=I8-0.1,"No ritmo",IF(H8&gt;=I8-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K8" s="33" t="n"/>
@@ -2399,7 +2414,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(OR(B9="",G9=""),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),IF(G9=0,0,MAX(0,F9/G9)))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),IF(F9=0,0,MAX(0,G9/F9))))))</f>
+        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
         <v>0.333333333333333</v>
       </c>
       <c r="I9" s="25">
@@ -2407,7 +2422,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J9" s="24" t="str">
-        <f>IF(OR(B9="",H9=""),"",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B9="","",IF(H9="","Faltam dados",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K9" s="33" t="inlineStr">
@@ -2444,7 +2459,7 @@
         <v>82</v>
       </c>
       <c r="H10" s="25">
-        <f>IF(OR(B10="",G10=""),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),IF(G10=0,0,MAX(0,F10/G10)))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),IF(F10=0,0,MAX(0,G10/F10))))))</f>
+        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
         <v>0.733333333333333</v>
       </c>
       <c r="I10" s="25">
@@ -2452,7 +2467,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J10" s="24" t="str">
-        <f>IF(OR(B10="",H10=""),"",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B10="","",IF(H10="","Faltam dados",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K10" s="33" t="inlineStr">
@@ -2471,7 +2486,7 @@
       <c r="F11" s="33" t="n"/>
       <c r="G11" s="33" t="n"/>
       <c r="H11" s="25">
-        <f>IF(OR(B11="",G11=""),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),IF(G11=0,0,MAX(0,F11/G11)))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),IF(F11=0,0,MAX(0,G11/F11))))))</f>
+        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
         <v/>
       </c>
       <c r="I11" s="25">
@@ -2479,7 +2494,7 @@
         <v/>
       </c>
       <c r="J11" s="24">
-        <f>IF(OR(B11="",H11=""),"",IF(H11&gt;=1,"Atingido",IF(H11&gt;=I11-0.1,"No ritmo",IF(H11&gt;=I11-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B11="","",IF(H11="","Faltam dados",IF(H11&gt;=1,"Atingido",IF(H11&gt;=I11-0.1,"No ritmo",IF(H11&gt;=I11-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K11" s="33" t="n"/>
@@ -2494,7 +2509,7 @@
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="33" t="n"/>
       <c r="H12" s="25">
-        <f>IF(OR(B12="",G12=""),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),IF(G12=0,0,MAX(0,F12/G12)))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),IF(F12=0,0,MAX(0,G12/F12))))))</f>
+        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
         <v/>
       </c>
       <c r="I12" s="25">
@@ -2502,7 +2517,7 @@
         <v/>
       </c>
       <c r="J12" s="24">
-        <f>IF(OR(B12="",H12=""),"",IF(H12&gt;=1,"Atingido",IF(H12&gt;=I12-0.1,"No ritmo",IF(H12&gt;=I12-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B12="","",IF(H12="","Faltam dados",IF(H12&gt;=1,"Atingido",IF(H12&gt;=I12-0.1,"No ritmo",IF(H12&gt;=I12-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K12" s="33" t="n"/>
@@ -2539,7 +2554,7 @@
         <v>2.8</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(OR(B13="",G13=""),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),IF(G13=0,0,MAX(0,F13/G13)))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),IF(F13=0,0,MAX(0,G13/F13))))))</f>
+        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
         <v>0.333333333333334</v>
       </c>
       <c r="I13" s="25">
@@ -2547,7 +2562,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J13" s="24" t="str">
-        <f>IF(OR(B13="",H13=""),"",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B13="","",IF(H13="","Faltam dados",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K13" s="33" t="inlineStr">
@@ -2584,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="H14" s="25">
-        <f>IF(OR(B14="",G14=""),"",IF(K14="Menor é melhor",IF(G14&lt;=F14,1,IF(E14&gt;F14,MAX(0,(E14-G14)/(E14-F14)),IF(G14=0,0,MAX(0,F14/G14)))),IF(G14&gt;=F14,1,IF(E14&lt;F14,MAX(0,(G14-E14)/(F14-E14)),IF(F14=0,0,MAX(0,G14/F14))))))</f>
+        <f>IF(B14="","",IF(OR(NOT(ISNUMBER(E14)),NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"",IF(K14="Menor é melhor",IF(G14&lt;=F14,1,IF(E14&gt;F14,MAX(0,(E14-G14)/(E14-F14)),MAX(0,1-(G14-F14)/MAX(ABS(F14),ABS(G14))))),IF(G14&gt;=F14,1,IF(E14&lt;F14,MAX(0,(G14-E14)/(F14-E14)),MAX(0,1-(F14-G14)/MAX(ABS(F14),ABS(G14))))))))</f>
         <v>0.8</v>
       </c>
       <c r="I14" s="25">
@@ -2592,7 +2607,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J14" s="24" t="str">
-        <f>IF(OR(B14="",H14=""),"",IF(H14&gt;=1,"Atingido",IF(H14&gt;=I14-0.1,"No ritmo",IF(H14&gt;=I14-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B14="","",IF(H14="","Faltam dados",IF(H14&gt;=1,"Atingido",IF(H14&gt;=I14-0.1,"No ritmo",IF(H14&gt;=I14-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K14" s="33" t="inlineStr">
@@ -2611,7 +2626,7 @@
       <c r="F15" s="33" t="n"/>
       <c r="G15" s="33" t="n"/>
       <c r="H15" s="25">
-        <f>IF(OR(B15="",G15=""),"",IF(K15="Menor é melhor",IF(G15&lt;=F15,1,IF(E15&gt;F15,MAX(0,(E15-G15)/(E15-F15)),IF(G15=0,0,MAX(0,F15/G15)))),IF(G15&gt;=F15,1,IF(E15&lt;F15,MAX(0,(G15-E15)/(F15-E15)),IF(F15=0,0,MAX(0,G15/F15))))))</f>
+        <f>IF(B15="","",IF(OR(NOT(ISNUMBER(E15)),NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"",IF(K15="Menor é melhor",IF(G15&lt;=F15,1,IF(E15&gt;F15,MAX(0,(E15-G15)/(E15-F15)),MAX(0,1-(G15-F15)/MAX(ABS(F15),ABS(G15))))),IF(G15&gt;=F15,1,IF(E15&lt;F15,MAX(0,(G15-E15)/(F15-E15)),MAX(0,1-(F15-G15)/MAX(ABS(F15),ABS(G15))))))))</f>
         <v/>
       </c>
       <c r="I15" s="25">
@@ -2619,7 +2634,7 @@
         <v/>
       </c>
       <c r="J15" s="24">
-        <f>IF(OR(B15="",H15=""),"",IF(H15&gt;=1,"Atingido",IF(H15&gt;=I15-0.1,"No ritmo",IF(H15&gt;=I15-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B15="","",IF(H15="","Faltam dados",IF(H15&gt;=1,"Atingido",IF(H15&gt;=I15-0.1,"No ritmo",IF(H15&gt;=I15-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K15" s="33" t="n"/>
@@ -2634,7 +2649,7 @@
       <c r="F16" s="33" t="n"/>
       <c r="G16" s="33" t="n"/>
       <c r="H16" s="25">
-        <f>IF(OR(B16="",G16=""),"",IF(K16="Menor é melhor",IF(G16&lt;=F16,1,IF(E16&gt;F16,MAX(0,(E16-G16)/(E16-F16)),IF(G16=0,0,MAX(0,F16/G16)))),IF(G16&gt;=F16,1,IF(E16&lt;F16,MAX(0,(G16-E16)/(F16-E16)),IF(F16=0,0,MAX(0,G16/F16))))))</f>
+        <f>IF(B16="","",IF(OR(NOT(ISNUMBER(E16)),NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"",IF(K16="Menor é melhor",IF(G16&lt;=F16,1,IF(E16&gt;F16,MAX(0,(E16-G16)/(E16-F16)),MAX(0,1-(G16-F16)/MAX(ABS(F16),ABS(G16))))),IF(G16&gt;=F16,1,IF(E16&lt;F16,MAX(0,(G16-E16)/(F16-E16)),MAX(0,1-(F16-G16)/MAX(ABS(F16),ABS(G16))))))))</f>
         <v/>
       </c>
       <c r="I16" s="25">
@@ -2642,7 +2657,7 @@
         <v/>
       </c>
       <c r="J16" s="24">
-        <f>IF(OR(B16="",H16=""),"",IF(H16&gt;=1,"Atingido",IF(H16&gt;=I16-0.1,"No ritmo",IF(H16&gt;=I16-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B16="","",IF(H16="","Faltam dados",IF(H16&gt;=1,"Atingido",IF(H16&gt;=I16-0.1,"No ritmo",IF(H16&gt;=I16-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K16" s="33" t="n"/>
@@ -2679,7 +2694,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="25">
-        <f>IF(OR(B17="",G17=""),"",IF(K17="Menor é melhor",IF(G17&lt;=F17,1,IF(E17&gt;F17,MAX(0,(E17-G17)/(E17-F17)),IF(G17=0,0,MAX(0,F17/G17)))),IF(G17&gt;=F17,1,IF(E17&lt;F17,MAX(0,(G17-E17)/(F17-E17)),IF(F17=0,0,MAX(0,G17/F17))))))</f>
+        <f>IF(B17="","",IF(OR(NOT(ISNUMBER(E17)),NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"",IF(K17="Menor é melhor",IF(G17&lt;=F17,1,IF(E17&gt;F17,MAX(0,(E17-G17)/(E17-F17)),MAX(0,1-(G17-F17)/MAX(ABS(F17),ABS(G17))))),IF(G17&gt;=F17,1,IF(E17&lt;F17,MAX(0,(G17-E17)/(F17-E17)),MAX(0,1-(F17-G17)/MAX(ABS(F17),ABS(G17))))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I17" s="25">
@@ -2687,7 +2702,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J17" s="24" t="str">
-        <f>IF(OR(B17="",H17=""),"",IF(H17&gt;=1,"Atingido",IF(H17&gt;=I17-0.1,"No ritmo",IF(H17&gt;=I17-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B17="","",IF(H17="","Faltam dados",IF(H17&gt;=1,"Atingido",IF(H17&gt;=I17-0.1,"No ritmo",IF(H17&gt;=I17-0.25,"Atenção","Em risco")))))</f>
         <v>Atenção</v>
       </c>
       <c r="K17" s="33" t="inlineStr">
@@ -2724,7 +2739,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="25">
-        <f>IF(OR(B18="",G18=""),"",IF(K18="Menor é melhor",IF(G18&lt;=F18,1,IF(E18&gt;F18,MAX(0,(E18-G18)/(E18-F18)),IF(G18=0,0,MAX(0,F18/G18)))),IF(G18&gt;=F18,1,IF(E18&lt;F18,MAX(0,(G18-E18)/(F18-E18)),IF(F18=0,0,MAX(0,G18/F18))))))</f>
+        <f>IF(B18="","",IF(OR(NOT(ISNUMBER(E18)),NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"",IF(K18="Menor é melhor",IF(G18&lt;=F18,1,IF(E18&gt;F18,MAX(0,(E18-G18)/(E18-F18)),MAX(0,1-(G18-F18)/MAX(ABS(F18),ABS(G18))))),IF(G18&gt;=F18,1,IF(E18&lt;F18,MAX(0,(G18-E18)/(F18-E18)),MAX(0,1-(F18-G18)/MAX(ABS(F18),ABS(G18))))))))</f>
         <v>0.5</v>
       </c>
       <c r="I18" s="25">
@@ -2732,7 +2747,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J18" s="24" t="str">
-        <f>IF(OR(B18="",H18=""),"",IF(H18&gt;=1,"Atingido",IF(H18&gt;=I18-0.1,"No ritmo",IF(H18&gt;=I18-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B18="","",IF(H18="","Faltam dados",IF(H18&gt;=1,"Atingido",IF(H18&gt;=I18-0.1,"No ritmo",IF(H18&gt;=I18-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K18" s="33" t="inlineStr">
@@ -2751,7 +2766,7 @@
       <c r="F19" s="33" t="n"/>
       <c r="G19" s="33" t="n"/>
       <c r="H19" s="25">
-        <f>IF(OR(B19="",G19=""),"",IF(K19="Menor é melhor",IF(G19&lt;=F19,1,IF(E19&gt;F19,MAX(0,(E19-G19)/(E19-F19)),IF(G19=0,0,MAX(0,F19/G19)))),IF(G19&gt;=F19,1,IF(E19&lt;F19,MAX(0,(G19-E19)/(F19-E19)),IF(F19=0,0,MAX(0,G19/F19))))))</f>
+        <f>IF(B19="","",IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"",IF(K19="Menor é melhor",IF(G19&lt;=F19,1,IF(E19&gt;F19,MAX(0,(E19-G19)/(E19-F19)),MAX(0,1-(G19-F19)/MAX(ABS(F19),ABS(G19))))),IF(G19&gt;=F19,1,IF(E19&lt;F19,MAX(0,(G19-E19)/(F19-E19)),MAX(0,1-(F19-G19)/MAX(ABS(F19),ABS(G19))))))))</f>
         <v/>
       </c>
       <c r="I19" s="25">
@@ -2759,7 +2774,7 @@
         <v/>
       </c>
       <c r="J19" s="24">
-        <f>IF(OR(B19="",H19=""),"",IF(H19&gt;=1,"Atingido",IF(H19&gt;=I19-0.1,"No ritmo",IF(H19&gt;=I19-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B19="","",IF(H19="","Faltam dados",IF(H19&gt;=1,"Atingido",IF(H19&gt;=I19-0.1,"No ritmo",IF(H19&gt;=I19-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K19" s="33" t="n"/>
@@ -2774,7 +2789,7 @@
       <c r="F20" s="33" t="n"/>
       <c r="G20" s="33" t="n"/>
       <c r="H20" s="25">
-        <f>IF(OR(B20="",G20=""),"",IF(K20="Menor é melhor",IF(G20&lt;=F20,1,IF(E20&gt;F20,MAX(0,(E20-G20)/(E20-F20)),IF(G20=0,0,MAX(0,F20/G20)))),IF(G20&gt;=F20,1,IF(E20&lt;F20,MAX(0,(G20-E20)/(F20-E20)),IF(F20=0,0,MAX(0,G20/F20))))))</f>
+        <f>IF(B20="","",IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20)),NOT(ISNUMBER(G20))),"",IF(K20="Menor é melhor",IF(G20&lt;=F20,1,IF(E20&gt;F20,MAX(0,(E20-G20)/(E20-F20)),MAX(0,1-(G20-F20)/MAX(ABS(F20),ABS(G20))))),IF(G20&gt;=F20,1,IF(E20&lt;F20,MAX(0,(G20-E20)/(F20-E20)),MAX(0,1-(F20-G20)/MAX(ABS(F20),ABS(G20))))))))</f>
         <v/>
       </c>
       <c r="I20" s="25">
@@ -2782,7 +2797,7 @@
         <v/>
       </c>
       <c r="J20" s="24">
-        <f>IF(OR(B20="",H20=""),"",IF(H20&gt;=1,"Atingido",IF(H20&gt;=I20-0.1,"No ritmo",IF(H20&gt;=I20-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B20="","",IF(H20="","Faltam dados",IF(H20&gt;=1,"Atingido",IF(H20&gt;=I20-0.1,"No ritmo",IF(H20&gt;=I20-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K20" s="33" t="n"/>
@@ -2797,7 +2812,7 @@
       <c r="F21" s="33" t="n"/>
       <c r="G21" s="33" t="n"/>
       <c r="H21" s="25">
-        <f>IF(OR(B21="",G21=""),"",IF(K21="Menor é melhor",IF(G21&lt;=F21,1,IF(E21&gt;F21,MAX(0,(E21-G21)/(E21-F21)),IF(G21=0,0,MAX(0,F21/G21)))),IF(G21&gt;=F21,1,IF(E21&lt;F21,MAX(0,(G21-E21)/(F21-E21)),IF(F21=0,0,MAX(0,G21/F21))))))</f>
+        <f>IF(B21="","",IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21)),NOT(ISNUMBER(G21))),"",IF(K21="Menor é melhor",IF(G21&lt;=F21,1,IF(E21&gt;F21,MAX(0,(E21-G21)/(E21-F21)),MAX(0,1-(G21-F21)/MAX(ABS(F21),ABS(G21))))),IF(G21&gt;=F21,1,IF(E21&lt;F21,MAX(0,(G21-E21)/(F21-E21)),MAX(0,1-(F21-G21)/MAX(ABS(F21),ABS(G21))))))))</f>
         <v/>
       </c>
       <c r="I21" s="25">
@@ -2805,7 +2820,7 @@
         <v/>
       </c>
       <c r="J21" s="24">
-        <f>IF(OR(B21="",H21=""),"",IF(H21&gt;=1,"Atingido",IF(H21&gt;=I21-0.1,"No ritmo",IF(H21&gt;=I21-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B21="","",IF(H21="","Faltam dados",IF(H21&gt;=1,"Atingido",IF(H21&gt;=I21-0.1,"No ritmo",IF(H21&gt;=I21-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K21" s="33" t="n"/>
@@ -2820,7 +2835,7 @@
       <c r="F22" s="33" t="n"/>
       <c r="G22" s="33" t="n"/>
       <c r="H22" s="25">
-        <f>IF(OR(B22="",G22=""),"",IF(K22="Menor é melhor",IF(G22&lt;=F22,1,IF(E22&gt;F22,MAX(0,(E22-G22)/(E22-F22)),IF(G22=0,0,MAX(0,F22/G22)))),IF(G22&gt;=F22,1,IF(E22&lt;F22,MAX(0,(G22-E22)/(F22-E22)),IF(F22=0,0,MAX(0,G22/F22))))))</f>
+        <f>IF(B22="","",IF(OR(NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22)),NOT(ISNUMBER(G22))),"",IF(K22="Menor é melhor",IF(G22&lt;=F22,1,IF(E22&gt;F22,MAX(0,(E22-G22)/(E22-F22)),MAX(0,1-(G22-F22)/MAX(ABS(F22),ABS(G22))))),IF(G22&gt;=F22,1,IF(E22&lt;F22,MAX(0,(G22-E22)/(F22-E22)),MAX(0,1-(F22-G22)/MAX(ABS(F22),ABS(G22))))))))</f>
         <v/>
       </c>
       <c r="I22" s="25">
@@ -2828,7 +2843,7 @@
         <v/>
       </c>
       <c r="J22" s="24">
-        <f>IF(OR(B22="",H22=""),"",IF(H22&gt;=1,"Atingido",IF(H22&gt;=I22-0.1,"No ritmo",IF(H22&gt;=I22-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B22="","",IF(H22="","Faltam dados",IF(H22&gt;=1,"Atingido",IF(H22&gt;=I22-0.1,"No ritmo",IF(H22&gt;=I22-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K22" s="33" t="n"/>
@@ -2843,7 +2858,7 @@
       <c r="F23" s="33" t="n"/>
       <c r="G23" s="33" t="n"/>
       <c r="H23" s="25">
-        <f>IF(OR(B23="",G23=""),"",IF(K23="Menor é melhor",IF(G23&lt;=F23,1,IF(E23&gt;F23,MAX(0,(E23-G23)/(E23-F23)),IF(G23=0,0,MAX(0,F23/G23)))),IF(G23&gt;=F23,1,IF(E23&lt;F23,MAX(0,(G23-E23)/(F23-E23)),IF(F23=0,0,MAX(0,G23/F23))))))</f>
+        <f>IF(B23="","",IF(OR(NOT(ISNUMBER(E23)),NOT(ISNUMBER(F23)),NOT(ISNUMBER(G23))),"",IF(K23="Menor é melhor",IF(G23&lt;=F23,1,IF(E23&gt;F23,MAX(0,(E23-G23)/(E23-F23)),MAX(0,1-(G23-F23)/MAX(ABS(F23),ABS(G23))))),IF(G23&gt;=F23,1,IF(E23&lt;F23,MAX(0,(G23-E23)/(F23-E23)),MAX(0,1-(F23-G23)/MAX(ABS(F23),ABS(G23))))))))</f>
         <v/>
       </c>
       <c r="I23" s="25">
@@ -2851,7 +2866,7 @@
         <v/>
       </c>
       <c r="J23" s="24">
-        <f>IF(OR(B23="",H23=""),"",IF(H23&gt;=1,"Atingido",IF(H23&gt;=I23-0.1,"No ritmo",IF(H23&gt;=I23-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B23="","",IF(H23="","Faltam dados",IF(H23&gt;=1,"Atingido",IF(H23&gt;=I23-0.1,"No ritmo",IF(H23&gt;=I23-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K23" s="33" t="n"/>
@@ -2866,7 +2881,7 @@
       <c r="F24" s="33" t="n"/>
       <c r="G24" s="33" t="n"/>
       <c r="H24" s="25">
-        <f>IF(OR(B24="",G24=""),"",IF(K24="Menor é melhor",IF(G24&lt;=F24,1,IF(E24&gt;F24,MAX(0,(E24-G24)/(E24-F24)),IF(G24=0,0,MAX(0,F24/G24)))),IF(G24&gt;=F24,1,IF(E24&lt;F24,MAX(0,(G24-E24)/(F24-E24)),IF(F24=0,0,MAX(0,G24/F24))))))</f>
+        <f>IF(B24="","",IF(OR(NOT(ISNUMBER(E24)),NOT(ISNUMBER(F24)),NOT(ISNUMBER(G24))),"",IF(K24="Menor é melhor",IF(G24&lt;=F24,1,IF(E24&gt;F24,MAX(0,(E24-G24)/(E24-F24)),MAX(0,1-(G24-F24)/MAX(ABS(F24),ABS(G24))))),IF(G24&gt;=F24,1,IF(E24&lt;F24,MAX(0,(G24-E24)/(F24-E24)),MAX(0,1-(F24-G24)/MAX(ABS(F24),ABS(G24))))))))</f>
         <v/>
       </c>
       <c r="I24" s="25">
@@ -2874,7 +2889,7 @@
         <v/>
       </c>
       <c r="J24" s="24">
-        <f>IF(OR(B24="",H24=""),"",IF(H24&gt;=1,"Atingido",IF(H24&gt;=I24-0.1,"No ritmo",IF(H24&gt;=I24-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B24="","",IF(H24="","Faltam dados",IF(H24&gt;=1,"Atingido",IF(H24&gt;=I24-0.1,"No ritmo",IF(H24&gt;=I24-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K24" s="33" t="n"/>
@@ -2883,7 +2898,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Progresso: valor atual no alvo = 100 %; fora do alvo, é o caminho andado entre o ponto de partida e a meta — e, quando o ponto de partida já estava dentro da meta (um teto ou piso a manter), é meta ÷ atual (16 horas extras para um teto de 8 = 50 %). Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso).</t>
+          <t>Progresso: só é calculado com ponto de partida, meta e valor atual preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso).</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2913,20 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="J5:J24">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="1">
       <formula>J5="Atingido"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="2">
       <formula>J5="No ritmo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>J5="Atenção"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="4">
       <formula>J5="Em risco"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>J5="Faltam dados"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -3702,7 +3720,7 @@
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:O4">
-    <cfRule type="expression" priority="1" dxfId="4">
+    <cfRule type="expression" priority="1" dxfId="5">
       <formula>COLUMN()-2=INDIRECT("Config!$B$9")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
-        <f>IFERROR(AVERAGEIFS(Metas!$H$5:$H$24,Metas!$B$5:$B$24,"&lt;&gt;"),0)</f>
+        <f>IF(COUNT(Metas!$H$5:$H$24)=0,"Faltam dados",AVERAGEIFS(Metas!$H$5:$H$24,Metas!$B$5:$B$24,"&lt;&gt;"))</f>
         <v>0.646296296296296</v>
       </c>
       <c r="H5" s="14" t="n"/>
@@ -1104,7 +1104,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="25">
-        <f>IF(OR(Metas!$A$5="",B9=0),"",AVERAGEIFS(Metas!$H$5:$H$8,Metas!$B$5:$B$8,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$5="",B9=0),"",IF(COUNT(Metas!$H$5:$H$8)=0,"Faltam dados",AVERAGEIFS(Metas!$H$5:$H$8,Metas!$B$5:$B$8,"&lt;&gt;")))</f>
         <v>0.816666666666667</v>
       </c>
       <c r="D9" s="24">
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="26" t="str">
-        <f>IF(C9="","",REPT("█",ROUND(C9*30,0)))</f>
+        <f>IF(ISNUMBER(C9),REPT("█",ROUND(C9*30,0)),"")</f>
         <v>█████████████████████████</v>
       </c>
       <c r="G9" s="21" t="n"/>
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="25">
-        <f>IF(OR(Metas!$A$9="",B10=0),"",AVERAGEIFS(Metas!$H$9:$H$12,Metas!$B$9:$B$12,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$9="",B10=0),"",IF(COUNT(Metas!$H$9:$H$12)=0,"Faltam dados",AVERAGEIFS(Metas!$H$9:$H$12,Metas!$B$9:$B$12,"&lt;&gt;")))</f>
         <v>0.533333333333333</v>
       </c>
       <c r="D10" s="24">
@@ -1144,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="26" t="str">
-        <f>IF(C10="","",REPT("█",ROUND(C10*30,0)))</f>
+        <f>IF(ISNUMBER(C10),REPT("█",ROUND(C10*30,0)),"")</f>
         <v>████████████████</v>
       </c>
       <c r="G10" s="21" t="n"/>
@@ -1160,7 +1160,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="25">
-        <f>IF(OR(Metas!$A$13="",B11=0),"",AVERAGEIFS(Metas!$H$13:$H$16,Metas!$B$13:$B$16,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$13="",B11=0),"",IF(COUNT(Metas!$H$13:$H$16)=0,"Faltam dados",AVERAGEIFS(Metas!$H$13:$H$16,Metas!$B$13:$B$16,"&lt;&gt;")))</f>
         <v>0.566666666666667</v>
       </c>
       <c r="D11" s="24">
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="26" t="str">
-        <f>IF(C11="","",REPT("█",ROUND(C11*30,0)))</f>
+        <f>IF(ISNUMBER(C11),REPT("█",ROUND(C11*30,0)),"")</f>
         <v>█████████████████</v>
       </c>
       <c r="G11" s="21" t="n"/>
@@ -1188,7 +1188,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="25">
-        <f>IF(OR(Metas!$A$17="",B12=0),"",AVERAGEIFS(Metas!$H$17:$H$20,Metas!$B$17:$B$20,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$17="",B12=0),"",IF(COUNT(Metas!$H$17:$H$20)=0,"Faltam dados",AVERAGEIFS(Metas!$H$17:$H$20,Metas!$B$17:$B$20,"&lt;&gt;")))</f>
         <v>0.583333333333333</v>
       </c>
       <c r="D12" s="24">
@@ -1200,7 +1200,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="26" t="str">
-        <f>IF(C12="","",REPT("█",ROUND(C12*30,0)))</f>
+        <f>IF(ISNUMBER(C12),REPT("█",ROUND(C12*30,0)),"")</f>
         <v>█████████████████</v>
       </c>
       <c r="G12" s="21" t="n"/>
@@ -1216,7 +1216,7 @@
         <v/>
       </c>
       <c r="C13" s="25">
-        <f>IF(OR(Metas!$A$21="",B13=0),"",AVERAGEIFS(Metas!$H$21:$H$24,Metas!$B$21:$B$24,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$21="",B13=0),"",IF(COUNT(Metas!$H$21:$H$24)=0,"Faltam dados",AVERAGEIFS(Metas!$H$21:$H$24,Metas!$B$21:$B$24,"&lt;&gt;")))</f>
         <v/>
       </c>
       <c r="D13" s="24">
@@ -1228,7 +1228,7 @@
         <v/>
       </c>
       <c r="F13" s="26">
-        <f>IF(C13="","",REPT("█",ROUND(C13*30,0)))</f>
+        <f>IF(ISNUMBER(C13),REPT("█",ROUND(C13*30,0)),"")</f>
         <v/>
       </c>
       <c r="G13" s="21" t="n"/>
@@ -2252,7 +2252,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
+        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5)),AND(K5&lt;&gt;"Menor é melhor",K5&lt;&gt;"Maior é melhor")),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I5" s="25">
@@ -2297,7 +2297,7 @@
         <v>27400</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
+        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6)),AND(K6&lt;&gt;"Menor é melhor",K6&lt;&gt;"Maior é melhor")),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
         <v>0.783333333333333</v>
       </c>
       <c r="I6" s="25">
@@ -2342,7 +2342,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
+        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7)),AND(K7&lt;&gt;"Menor é melhor",K7&lt;&gt;"Maior é melhor")),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
         <v>1</v>
       </c>
       <c r="I7" s="25">
@@ -2369,7 +2369,7 @@
       <c r="F8" s="33" t="n"/>
       <c r="G8" s="33" t="n"/>
       <c r="H8" s="25">
-        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
+        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8)),AND(K8&lt;&gt;"Menor é melhor",K8&lt;&gt;"Maior é melhor")),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
         <v/>
       </c>
       <c r="I8" s="25">
@@ -2414,7 +2414,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
+        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9)),AND(K9&lt;&gt;"Menor é melhor",K9&lt;&gt;"Maior é melhor")),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
         <v>0.333333333333333</v>
       </c>
       <c r="I9" s="25">
@@ -2459,7 +2459,7 @@
         <v>82</v>
       </c>
       <c r="H10" s="25">
-        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
+        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10)),AND(K10&lt;&gt;"Menor é melhor",K10&lt;&gt;"Maior é melhor")),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
         <v>0.733333333333333</v>
       </c>
       <c r="I10" s="25">
@@ -2486,7 +2486,7 @@
       <c r="F11" s="33" t="n"/>
       <c r="G11" s="33" t="n"/>
       <c r="H11" s="25">
-        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
+        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11)),AND(K11&lt;&gt;"Menor é melhor",K11&lt;&gt;"Maior é melhor")),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
         <v/>
       </c>
       <c r="I11" s="25">
@@ -2509,7 +2509,7 @@
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="33" t="n"/>
       <c r="H12" s="25">
-        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
+        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12)),AND(K12&lt;&gt;"Menor é melhor",K12&lt;&gt;"Maior é melhor")),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
         <v/>
       </c>
       <c r="I12" s="25">
@@ -2554,7 +2554,7 @@
         <v>2.8</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
+        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13)),AND(K13&lt;&gt;"Menor é melhor",K13&lt;&gt;"Maior é melhor")),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
         <v>0.333333333333334</v>
       </c>
       <c r="I13" s="25">
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="H14" s="25">
-        <f>IF(B14="","",IF(OR(NOT(ISNUMBER(E14)),NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"",IF(K14="Menor é melhor",IF(G14&lt;=F14,1,IF(E14&gt;F14,MAX(0,(E14-G14)/(E14-F14)),MAX(0,1-(G14-F14)/MAX(ABS(F14),ABS(G14))))),IF(G14&gt;=F14,1,IF(E14&lt;F14,MAX(0,(G14-E14)/(F14-E14)),MAX(0,1-(F14-G14)/MAX(ABS(F14),ABS(G14))))))))</f>
+        <f>IF(B14="","",IF(OR(NOT(ISNUMBER(E14)),NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14)),AND(K14&lt;&gt;"Menor é melhor",K14&lt;&gt;"Maior é melhor")),"",IF(K14="Menor é melhor",IF(G14&lt;=F14,1,IF(E14&gt;F14,MAX(0,(E14-G14)/(E14-F14)),MAX(0,1-(G14-F14)/MAX(ABS(F14),ABS(G14))))),IF(G14&gt;=F14,1,IF(E14&lt;F14,MAX(0,(G14-E14)/(F14-E14)),MAX(0,1-(F14-G14)/MAX(ABS(F14),ABS(G14))))))))</f>
         <v>0.8</v>
       </c>
       <c r="I14" s="25">
@@ -2626,7 +2626,7 @@
       <c r="F15" s="33" t="n"/>
       <c r="G15" s="33" t="n"/>
       <c r="H15" s="25">
-        <f>IF(B15="","",IF(OR(NOT(ISNUMBER(E15)),NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"",IF(K15="Menor é melhor",IF(G15&lt;=F15,1,IF(E15&gt;F15,MAX(0,(E15-G15)/(E15-F15)),MAX(0,1-(G15-F15)/MAX(ABS(F15),ABS(G15))))),IF(G15&gt;=F15,1,IF(E15&lt;F15,MAX(0,(G15-E15)/(F15-E15)),MAX(0,1-(F15-G15)/MAX(ABS(F15),ABS(G15))))))))</f>
+        <f>IF(B15="","",IF(OR(NOT(ISNUMBER(E15)),NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15)),AND(K15&lt;&gt;"Menor é melhor",K15&lt;&gt;"Maior é melhor")),"",IF(K15="Menor é melhor",IF(G15&lt;=F15,1,IF(E15&gt;F15,MAX(0,(E15-G15)/(E15-F15)),MAX(0,1-(G15-F15)/MAX(ABS(F15),ABS(G15))))),IF(G15&gt;=F15,1,IF(E15&lt;F15,MAX(0,(G15-E15)/(F15-E15)),MAX(0,1-(F15-G15)/MAX(ABS(F15),ABS(G15))))))))</f>
         <v/>
       </c>
       <c r="I15" s="25">
@@ -2649,7 +2649,7 @@
       <c r="F16" s="33" t="n"/>
       <c r="G16" s="33" t="n"/>
       <c r="H16" s="25">
-        <f>IF(B16="","",IF(OR(NOT(ISNUMBER(E16)),NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"",IF(K16="Menor é melhor",IF(G16&lt;=F16,1,IF(E16&gt;F16,MAX(0,(E16-G16)/(E16-F16)),MAX(0,1-(G16-F16)/MAX(ABS(F16),ABS(G16))))),IF(G16&gt;=F16,1,IF(E16&lt;F16,MAX(0,(G16-E16)/(F16-E16)),MAX(0,1-(F16-G16)/MAX(ABS(F16),ABS(G16))))))))</f>
+        <f>IF(B16="","",IF(OR(NOT(ISNUMBER(E16)),NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16)),AND(K16&lt;&gt;"Menor é melhor",K16&lt;&gt;"Maior é melhor")),"",IF(K16="Menor é melhor",IF(G16&lt;=F16,1,IF(E16&gt;F16,MAX(0,(E16-G16)/(E16-F16)),MAX(0,1-(G16-F16)/MAX(ABS(F16),ABS(G16))))),IF(G16&gt;=F16,1,IF(E16&lt;F16,MAX(0,(G16-E16)/(F16-E16)),MAX(0,1-(F16-G16)/MAX(ABS(F16),ABS(G16))))))))</f>
         <v/>
       </c>
       <c r="I16" s="25">
@@ -2694,7 +2694,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="25">
-        <f>IF(B17="","",IF(OR(NOT(ISNUMBER(E17)),NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"",IF(K17="Menor é melhor",IF(G17&lt;=F17,1,IF(E17&gt;F17,MAX(0,(E17-G17)/(E17-F17)),MAX(0,1-(G17-F17)/MAX(ABS(F17),ABS(G17))))),IF(G17&gt;=F17,1,IF(E17&lt;F17,MAX(0,(G17-E17)/(F17-E17)),MAX(0,1-(F17-G17)/MAX(ABS(F17),ABS(G17))))))))</f>
+        <f>IF(B17="","",IF(OR(NOT(ISNUMBER(E17)),NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17)),AND(K17&lt;&gt;"Menor é melhor",K17&lt;&gt;"Maior é melhor")),"",IF(K17="Menor é melhor",IF(G17&lt;=F17,1,IF(E17&gt;F17,MAX(0,(E17-G17)/(E17-F17)),MAX(0,1-(G17-F17)/MAX(ABS(F17),ABS(G17))))),IF(G17&gt;=F17,1,IF(E17&lt;F17,MAX(0,(G17-E17)/(F17-E17)),MAX(0,1-(F17-G17)/MAX(ABS(F17),ABS(G17))))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I17" s="25">
@@ -2739,7 +2739,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="25">
-        <f>IF(B18="","",IF(OR(NOT(ISNUMBER(E18)),NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"",IF(K18="Menor é melhor",IF(G18&lt;=F18,1,IF(E18&gt;F18,MAX(0,(E18-G18)/(E18-F18)),MAX(0,1-(G18-F18)/MAX(ABS(F18),ABS(G18))))),IF(G18&gt;=F18,1,IF(E18&lt;F18,MAX(0,(G18-E18)/(F18-E18)),MAX(0,1-(F18-G18)/MAX(ABS(F18),ABS(G18))))))))</f>
+        <f>IF(B18="","",IF(OR(NOT(ISNUMBER(E18)),NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18)),AND(K18&lt;&gt;"Menor é melhor",K18&lt;&gt;"Maior é melhor")),"",IF(K18="Menor é melhor",IF(G18&lt;=F18,1,IF(E18&gt;F18,MAX(0,(E18-G18)/(E18-F18)),MAX(0,1-(G18-F18)/MAX(ABS(F18),ABS(G18))))),IF(G18&gt;=F18,1,IF(E18&lt;F18,MAX(0,(G18-E18)/(F18-E18)),MAX(0,1-(F18-G18)/MAX(ABS(F18),ABS(G18))))))))</f>
         <v>0.5</v>
       </c>
       <c r="I18" s="25">
@@ -2766,7 +2766,7 @@
       <c r="F19" s="33" t="n"/>
       <c r="G19" s="33" t="n"/>
       <c r="H19" s="25">
-        <f>IF(B19="","",IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"",IF(K19="Menor é melhor",IF(G19&lt;=F19,1,IF(E19&gt;F19,MAX(0,(E19-G19)/(E19-F19)),MAX(0,1-(G19-F19)/MAX(ABS(F19),ABS(G19))))),IF(G19&gt;=F19,1,IF(E19&lt;F19,MAX(0,(G19-E19)/(F19-E19)),MAX(0,1-(F19-G19)/MAX(ABS(F19),ABS(G19))))))))</f>
+        <f>IF(B19="","",IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19)),AND(K19&lt;&gt;"Menor é melhor",K19&lt;&gt;"Maior é melhor")),"",IF(K19="Menor é melhor",IF(G19&lt;=F19,1,IF(E19&gt;F19,MAX(0,(E19-G19)/(E19-F19)),MAX(0,1-(G19-F19)/MAX(ABS(F19),ABS(G19))))),IF(G19&gt;=F19,1,IF(E19&lt;F19,MAX(0,(G19-E19)/(F19-E19)),MAX(0,1-(F19-G19)/MAX(ABS(F19),ABS(G19))))))))</f>
         <v/>
       </c>
       <c r="I19" s="25">
@@ -2789,7 +2789,7 @@
       <c r="F20" s="33" t="n"/>
       <c r="G20" s="33" t="n"/>
       <c r="H20" s="25">
-        <f>IF(B20="","",IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20)),NOT(ISNUMBER(G20))),"",IF(K20="Menor é melhor",IF(G20&lt;=F20,1,IF(E20&gt;F20,MAX(0,(E20-G20)/(E20-F20)),MAX(0,1-(G20-F20)/MAX(ABS(F20),ABS(G20))))),IF(G20&gt;=F20,1,IF(E20&lt;F20,MAX(0,(G20-E20)/(F20-E20)),MAX(0,1-(F20-G20)/MAX(ABS(F20),ABS(G20))))))))</f>
+        <f>IF(B20="","",IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20)),NOT(ISNUMBER(G20)),AND(K20&lt;&gt;"Menor é melhor",K20&lt;&gt;"Maior é melhor")),"",IF(K20="Menor é melhor",IF(G20&lt;=F20,1,IF(E20&gt;F20,MAX(0,(E20-G20)/(E20-F20)),MAX(0,1-(G20-F20)/MAX(ABS(F20),ABS(G20))))),IF(G20&gt;=F20,1,IF(E20&lt;F20,MAX(0,(G20-E20)/(F20-E20)),MAX(0,1-(F20-G20)/MAX(ABS(F20),ABS(G20))))))))</f>
         <v/>
       </c>
       <c r="I20" s="25">
@@ -2812,7 +2812,7 @@
       <c r="F21" s="33" t="n"/>
       <c r="G21" s="33" t="n"/>
       <c r="H21" s="25">
-        <f>IF(B21="","",IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21)),NOT(ISNUMBER(G21))),"",IF(K21="Menor é melhor",IF(G21&lt;=F21,1,IF(E21&gt;F21,MAX(0,(E21-G21)/(E21-F21)),MAX(0,1-(G21-F21)/MAX(ABS(F21),ABS(G21))))),IF(G21&gt;=F21,1,IF(E21&lt;F21,MAX(0,(G21-E21)/(F21-E21)),MAX(0,1-(F21-G21)/MAX(ABS(F21),ABS(G21))))))))</f>
+        <f>IF(B21="","",IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21)),NOT(ISNUMBER(G21)),AND(K21&lt;&gt;"Menor é melhor",K21&lt;&gt;"Maior é melhor")),"",IF(K21="Menor é melhor",IF(G21&lt;=F21,1,IF(E21&gt;F21,MAX(0,(E21-G21)/(E21-F21)),MAX(0,1-(G21-F21)/MAX(ABS(F21),ABS(G21))))),IF(G21&gt;=F21,1,IF(E21&lt;F21,MAX(0,(G21-E21)/(F21-E21)),MAX(0,1-(F21-G21)/MAX(ABS(F21),ABS(G21))))))))</f>
         <v/>
       </c>
       <c r="I21" s="25">
@@ -2835,7 +2835,7 @@
       <c r="F22" s="33" t="n"/>
       <c r="G22" s="33" t="n"/>
       <c r="H22" s="25">
-        <f>IF(B22="","",IF(OR(NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22)),NOT(ISNUMBER(G22))),"",IF(K22="Menor é melhor",IF(G22&lt;=F22,1,IF(E22&gt;F22,MAX(0,(E22-G22)/(E22-F22)),MAX(0,1-(G22-F22)/MAX(ABS(F22),ABS(G22))))),IF(G22&gt;=F22,1,IF(E22&lt;F22,MAX(0,(G22-E22)/(F22-E22)),MAX(0,1-(F22-G22)/MAX(ABS(F22),ABS(G22))))))))</f>
+        <f>IF(B22="","",IF(OR(NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22)),NOT(ISNUMBER(G22)),AND(K22&lt;&gt;"Menor é melhor",K22&lt;&gt;"Maior é melhor")),"",IF(K22="Menor é melhor",IF(G22&lt;=F22,1,IF(E22&gt;F22,MAX(0,(E22-G22)/(E22-F22)),MAX(0,1-(G22-F22)/MAX(ABS(F22),ABS(G22))))),IF(G22&gt;=F22,1,IF(E22&lt;F22,MAX(0,(G22-E22)/(F22-E22)),MAX(0,1-(F22-G22)/MAX(ABS(F22),ABS(G22))))))))</f>
         <v/>
       </c>
       <c r="I22" s="25">
@@ -2858,7 +2858,7 @@
       <c r="F23" s="33" t="n"/>
       <c r="G23" s="33" t="n"/>
       <c r="H23" s="25">
-        <f>IF(B23="","",IF(OR(NOT(ISNUMBER(E23)),NOT(ISNUMBER(F23)),NOT(ISNUMBER(G23))),"",IF(K23="Menor é melhor",IF(G23&lt;=F23,1,IF(E23&gt;F23,MAX(0,(E23-G23)/(E23-F23)),MAX(0,1-(G23-F23)/MAX(ABS(F23),ABS(G23))))),IF(G23&gt;=F23,1,IF(E23&lt;F23,MAX(0,(G23-E23)/(F23-E23)),MAX(0,1-(F23-G23)/MAX(ABS(F23),ABS(G23))))))))</f>
+        <f>IF(B23="","",IF(OR(NOT(ISNUMBER(E23)),NOT(ISNUMBER(F23)),NOT(ISNUMBER(G23)),AND(K23&lt;&gt;"Menor é melhor",K23&lt;&gt;"Maior é melhor")),"",IF(K23="Menor é melhor",IF(G23&lt;=F23,1,IF(E23&gt;F23,MAX(0,(E23-G23)/(E23-F23)),MAX(0,1-(G23-F23)/MAX(ABS(F23),ABS(G23))))),IF(G23&gt;=F23,1,IF(E23&lt;F23,MAX(0,(G23-E23)/(F23-E23)),MAX(0,1-(F23-G23)/MAX(ABS(F23),ABS(G23))))))))</f>
         <v/>
       </c>
       <c r="I23" s="25">
@@ -2881,7 +2881,7 @@
       <c r="F24" s="33" t="n"/>
       <c r="G24" s="33" t="n"/>
       <c r="H24" s="25">
-        <f>IF(B24="","",IF(OR(NOT(ISNUMBER(E24)),NOT(ISNUMBER(F24)),NOT(ISNUMBER(G24))),"",IF(K24="Menor é melhor",IF(G24&lt;=F24,1,IF(E24&gt;F24,MAX(0,(E24-G24)/(E24-F24)),MAX(0,1-(G24-F24)/MAX(ABS(F24),ABS(G24))))),IF(G24&gt;=F24,1,IF(E24&lt;F24,MAX(0,(G24-E24)/(F24-E24)),MAX(0,1-(F24-G24)/MAX(ABS(F24),ABS(G24))))))))</f>
+        <f>IF(B24="","",IF(OR(NOT(ISNUMBER(E24)),NOT(ISNUMBER(F24)),NOT(ISNUMBER(G24)),AND(K24&lt;&gt;"Menor é melhor",K24&lt;&gt;"Maior é melhor")),"",IF(K24="Menor é melhor",IF(G24&lt;=F24,1,IF(E24&gt;F24,MAX(0,(E24-G24)/(E24-F24)),MAX(0,1-(G24-F24)/MAX(ABS(F24),ABS(G24))))),IF(G24&gt;=F24,1,IF(E24&lt;F24,MAX(0,(G24-E24)/(F24-E24)),MAX(0,1-(F24-G24)/MAX(ABS(F24),ABS(G24))))))))</f>
         <v/>
       </c>
       <c r="I24" s="25">
@@ -2898,7 +2898,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Progresso: só é calculado com ponto de partida, meta e valor atual preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso).</t>
+          <t>Progresso: só é calculado com ponto de partida, meta, valor atual e sentido preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens; sem nenhuma medição, a média do Painel também diz "Faltam dados"). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -1293,11 +1293,11 @@
         <v>Ana</v>
       </c>
       <c r="C17" s="27">
-        <f>IF(Metas!B5="","",Metas!G5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!G5))),"",Metas!G5)</f>
         <v>2</v>
       </c>
       <c r="D17" s="27">
-        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!F5))),"",Metas!F5)</f>
         <v>3</v>
       </c>
       <c r="E17" s="25">
@@ -1327,11 +1327,11 @@
         <v>Ana</v>
       </c>
       <c r="C18" s="27">
-        <f>IF(Metas!B6="","",Metas!G6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!G6))),"",Metas!G6)</f>
         <v>27400</v>
       </c>
       <c r="D18" s="27">
-        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!F6))),"",Metas!F6)</f>
         <v>30000</v>
       </c>
       <c r="E18" s="25">
@@ -1361,11 +1361,11 @@
         <v>Carla</v>
       </c>
       <c r="C19" s="27">
-        <f>IF(Metas!B7="","",Metas!G7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!G7))),"",Metas!G7)</f>
         <v>24</v>
       </c>
       <c r="D19" s="27">
-        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!F7))),"",Metas!F7)</f>
         <v>24</v>
       </c>
       <c r="E19" s="25">
@@ -1395,11 +1395,11 @@
         <v/>
       </c>
       <c r="C20" s="27">
-        <f>IF(Metas!B8="","",Metas!G8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!G8))),"",Metas!G8)</f>
         <v/>
       </c>
       <c r="D20" s="27">
-        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!F8))),"",Metas!F8)</f>
         <v/>
       </c>
       <c r="E20" s="25">
@@ -1429,11 +1429,11 @@
         <v>Ana</v>
       </c>
       <c r="C21" s="27">
-        <f>IF(Metas!B9="","",Metas!G9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!G9))),"",Metas!G9)</f>
         <v>3</v>
       </c>
       <c r="D21" s="27">
-        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!F9))),"",Metas!F9)</f>
         <v>1</v>
       </c>
       <c r="E21" s="25">
@@ -1463,11 +1463,11 @@
         <v>Bruno</v>
       </c>
       <c r="C22" s="27">
-        <f>IF(Metas!B10="","",Metas!G10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!G10))),"",Metas!G10)</f>
         <v>82</v>
       </c>
       <c r="D22" s="27">
-        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!F10))),"",Metas!F10)</f>
         <v>90</v>
       </c>
       <c r="E22" s="25">
@@ -1497,11 +1497,11 @@
         <v/>
       </c>
       <c r="C23" s="27">
-        <f>IF(Metas!B11="","",Metas!G11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!G11))),"",Metas!G11)</f>
         <v/>
       </c>
       <c r="D23" s="27">
-        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!F11))),"",Metas!F11)</f>
         <v/>
       </c>
       <c r="E23" s="25">
@@ -1531,11 +1531,11 @@
         <v/>
       </c>
       <c r="C24" s="27">
-        <f>IF(Metas!B12="","",Metas!G12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!G12))),"",Metas!G12)</f>
         <v/>
       </c>
       <c r="D24" s="27">
-        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!F12))),"",Metas!F12)</f>
         <v/>
       </c>
       <c r="E24" s="25">
@@ -1565,11 +1565,11 @@
         <v>Bruno</v>
       </c>
       <c r="C25" s="27">
-        <f>IF(Metas!B13="","",Metas!G13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!G13))),"",Metas!G13)</f>
         <v>2.8</v>
       </c>
       <c r="D25" s="27">
-        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!F13))),"",Metas!F13)</f>
         <v>2</v>
       </c>
       <c r="E25" s="25">
@@ -1599,11 +1599,11 @@
         <v>Carla</v>
       </c>
       <c r="C26" s="27">
-        <f>IF(Metas!B14="","",Metas!G14)</f>
+        <f>IF(OR(Metas!B14="",NOT(ISNUMBER(Metas!G14))),"",Metas!G14)</f>
         <v>60</v>
       </c>
       <c r="D26" s="27">
-        <f>IF(Metas!B14="","",Metas!F14)</f>
+        <f>IF(OR(Metas!B14="",NOT(ISNUMBER(Metas!F14))),"",Metas!F14)</f>
         <v>65</v>
       </c>
       <c r="E26" s="25">
@@ -1633,11 +1633,11 @@
         <v/>
       </c>
       <c r="C27" s="27">
-        <f>IF(Metas!B15="","",Metas!G15)</f>
+        <f>IF(OR(Metas!B15="",NOT(ISNUMBER(Metas!G15))),"",Metas!G15)</f>
         <v/>
       </c>
       <c r="D27" s="27">
-        <f>IF(Metas!B15="","",Metas!F15)</f>
+        <f>IF(OR(Metas!B15="",NOT(ISNUMBER(Metas!F15))),"",Metas!F15)</f>
         <v/>
       </c>
       <c r="E27" s="25">
@@ -1667,11 +1667,11 @@
         <v/>
       </c>
       <c r="C28" s="27">
-        <f>IF(Metas!B16="","",Metas!G16)</f>
+        <f>IF(OR(Metas!B16="",NOT(ISNUMBER(Metas!G16))),"",Metas!G16)</f>
         <v/>
       </c>
       <c r="D28" s="27">
-        <f>IF(Metas!B16="","",Metas!F16)</f>
+        <f>IF(OR(Metas!B16="",NOT(ISNUMBER(Metas!F16))),"",Metas!F16)</f>
         <v/>
       </c>
       <c r="E28" s="25">
@@ -1701,11 +1701,11 @@
         <v>Ana</v>
       </c>
       <c r="C29" s="27">
-        <f>IF(Metas!B17="","",Metas!G17)</f>
+        <f>IF(OR(Metas!B17="",NOT(ISNUMBER(Metas!G17))),"",Metas!G17)</f>
         <v>2</v>
       </c>
       <c r="D29" s="27">
-        <f>IF(Metas!B17="","",Metas!F17)</f>
+        <f>IF(OR(Metas!B17="",NOT(ISNUMBER(Metas!F17))),"",Metas!F17)</f>
         <v>3</v>
       </c>
       <c r="E29" s="25">
@@ -1735,11 +1735,11 @@
         <v>Ana</v>
       </c>
       <c r="C30" s="27">
-        <f>IF(Metas!B18="","",Metas!G18)</f>
+        <f>IF(OR(Metas!B18="",NOT(ISNUMBER(Metas!G18))),"",Metas!G18)</f>
         <v>14</v>
       </c>
       <c r="D30" s="27">
-        <f>IF(Metas!B18="","",Metas!F18)</f>
+        <f>IF(OR(Metas!B18="",NOT(ISNUMBER(Metas!F18))),"",Metas!F18)</f>
         <v>8</v>
       </c>
       <c r="E30" s="25">
@@ -1769,11 +1769,11 @@
         <v/>
       </c>
       <c r="C31" s="27">
-        <f>IF(Metas!B19="","",Metas!G19)</f>
+        <f>IF(OR(Metas!B19="",NOT(ISNUMBER(Metas!G19))),"",Metas!G19)</f>
         <v/>
       </c>
       <c r="D31" s="27">
-        <f>IF(Metas!B19="","",Metas!F19)</f>
+        <f>IF(OR(Metas!B19="",NOT(ISNUMBER(Metas!F19))),"",Metas!F19)</f>
         <v/>
       </c>
       <c r="E31" s="25">
@@ -1803,11 +1803,11 @@
         <v/>
       </c>
       <c r="C32" s="27">
-        <f>IF(Metas!B20="","",Metas!G20)</f>
+        <f>IF(OR(Metas!B20="",NOT(ISNUMBER(Metas!G20))),"",Metas!G20)</f>
         <v/>
       </c>
       <c r="D32" s="27">
-        <f>IF(Metas!B20="","",Metas!F20)</f>
+        <f>IF(OR(Metas!B20="",NOT(ISNUMBER(Metas!F20))),"",Metas!F20)</f>
         <v/>
       </c>
       <c r="E32" s="25">
@@ -1837,11 +1837,11 @@
         <v/>
       </c>
       <c r="C33" s="27">
-        <f>IF(Metas!B21="","",Metas!G21)</f>
+        <f>IF(OR(Metas!B21="",NOT(ISNUMBER(Metas!G21))),"",Metas!G21)</f>
         <v/>
       </c>
       <c r="D33" s="27">
-        <f>IF(Metas!B21="","",Metas!F21)</f>
+        <f>IF(OR(Metas!B21="",NOT(ISNUMBER(Metas!F21))),"",Metas!F21)</f>
         <v/>
       </c>
       <c r="E33" s="25">
@@ -1871,11 +1871,11 @@
         <v/>
       </c>
       <c r="C34" s="27">
-        <f>IF(Metas!B22="","",Metas!G22)</f>
+        <f>IF(OR(Metas!B22="",NOT(ISNUMBER(Metas!G22))),"",Metas!G22)</f>
         <v/>
       </c>
       <c r="D34" s="27">
-        <f>IF(Metas!B22="","",Metas!F22)</f>
+        <f>IF(OR(Metas!B22="",NOT(ISNUMBER(Metas!F22))),"",Metas!F22)</f>
         <v/>
       </c>
       <c r="E34" s="25">
@@ -1905,11 +1905,11 @@
         <v/>
       </c>
       <c r="C35" s="27">
-        <f>IF(Metas!B23="","",Metas!G23)</f>
+        <f>IF(OR(Metas!B23="",NOT(ISNUMBER(Metas!G23))),"",Metas!G23)</f>
         <v/>
       </c>
       <c r="D35" s="27">
-        <f>IF(Metas!B23="","",Metas!F23)</f>
+        <f>IF(OR(Metas!B23="",NOT(ISNUMBER(Metas!F23))),"",Metas!F23)</f>
         <v/>
       </c>
       <c r="E35" s="25">
@@ -1939,11 +1939,11 @@
         <v/>
       </c>
       <c r="C36" s="27">
-        <f>IF(Metas!B24="","",Metas!G24)</f>
+        <f>IF(OR(Metas!B24="",NOT(ISNUMBER(Metas!G24))),"",Metas!G24)</f>
         <v/>
       </c>
       <c r="D36" s="27">
-        <f>IF(Metas!B24="","",Metas!F24)</f>
+        <f>IF(OR(Metas!B24="",NOT(ISNUMBER(Metas!F24))),"",Metas!F24)</f>
         <v/>
       </c>
       <c r="E36" s="25">
@@ -3062,7 +3062,7 @@
         <v>Fechar 3 contratos mensais novos</v>
       </c>
       <c r="B5" s="24">
-        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!F5))),"",Metas!F5)</f>
         <v>3</v>
       </c>
       <c r="C5" s="33" t="n">
@@ -3107,7 +3107,7 @@
         <v>Receita recorrente mensal de R$ 30 mil</v>
       </c>
       <c r="B6" s="24">
-        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!F6))),"",Metas!F6)</f>
         <v>30000</v>
       </c>
       <c r="C6" s="33" t="n">
@@ -3152,7 +3152,7 @@
         <v>Propostas enviadas no trimestre</v>
       </c>
       <c r="B7" s="24">
-        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!F7))),"",Metas!F7)</f>
         <v>24</v>
       </c>
       <c r="C7" s="33" t="n">
@@ -3197,7 +3197,7 @@
         <v/>
       </c>
       <c r="B8" s="24">
-        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!F8))),"",Metas!F8)</f>
         <v/>
       </c>
       <c r="C8" s="33" t="n"/>
@@ -3220,7 +3220,7 @@
         <v>Etapas atrasadas por semana (média)</v>
       </c>
       <c r="B9" s="24">
-        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!F9))),"",Metas!F9)</f>
         <v>1</v>
       </c>
       <c r="C9" s="33" t="n">
@@ -3265,7 +3265,7 @@
         <v>Projetos entregues na data combinada</v>
       </c>
       <c r="B10" s="24">
-        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!F10))),"",Metas!F10)</f>
         <v>90</v>
       </c>
       <c r="C10" s="33" t="n">
@@ -3310,7 +3310,7 @@
         <v/>
       </c>
       <c r="B11" s="24">
-        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!F11))),"",Metas!F11)</f>
         <v/>
       </c>
       <c r="C11" s="33" t="n"/>
@@ -3333,7 +3333,7 @@
         <v/>
       </c>
       <c r="B12" s="24">
-        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!F12))),"",Metas!F12)</f>
         <v/>
       </c>
       <c r="C12" s="33" t="n"/>
@@ -3356,7 +3356,7 @@
         <v>Rodadas de revisão por peça (média)</v>
       </c>
       <c r="B13" s="24">
-        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!F13))),"",Metas!F13)</f>
         <v>2</v>
       </c>
       <c r="C13" s="33" t="n">
@@ -3401,7 +3401,7 @@
         <v>Peças aprovadas de primeira</v>
       </c>
       <c r="B14" s="24">
-        <f>IF(Metas!B14="","",Metas!F14)</f>
+        <f>IF(OR(Metas!B14="",NOT(ISNUMBER(Metas!F14))),"",Metas!F14)</f>
         <v>65</v>
       </c>
       <c r="C14" s="33" t="n">
@@ -3446,7 +3446,7 @@
         <v/>
       </c>
       <c r="B15" s="24">
-        <f>IF(Metas!B15="","",Metas!F15)</f>
+        <f>IF(OR(Metas!B15="",NOT(ISNUMBER(Metas!F15))),"",Metas!F15)</f>
         <v/>
       </c>
       <c r="C15" s="33" t="n"/>
@@ -3469,7 +3469,7 @@
         <v/>
       </c>
       <c r="B16" s="24">
-        <f>IF(Metas!B16="","",Metas!F16)</f>
+        <f>IF(OR(Metas!B16="",NOT(ISNUMBER(Metas!F16))),"",Metas!F16)</f>
         <v/>
       </c>
       <c r="C16" s="33" t="n"/>
@@ -3492,7 +3492,7 @@
         <v>Relatório mensal enviado até o dia 5</v>
       </c>
       <c r="B17" s="24">
-        <f>IF(Metas!B17="","",Metas!F17)</f>
+        <f>IF(OR(Metas!B17="",NOT(ISNUMBER(Metas!F17))),"",Metas!F17)</f>
         <v>3</v>
       </c>
       <c r="C17" s="33" t="n">
@@ -3537,7 +3537,7 @@
         <v>Horas extras da equipe no mês</v>
       </c>
       <c r="B18" s="24">
-        <f>IF(Metas!B18="","",Metas!F18)</f>
+        <f>IF(OR(Metas!B18="",NOT(ISNUMBER(Metas!F18))),"",Metas!F18)</f>
         <v>8</v>
       </c>
       <c r="C18" s="33" t="n">
@@ -3582,7 +3582,7 @@
         <v/>
       </c>
       <c r="B19" s="24">
-        <f>IF(Metas!B19="","",Metas!F19)</f>
+        <f>IF(OR(Metas!B19="",NOT(ISNUMBER(Metas!F19))),"",Metas!F19)</f>
         <v/>
       </c>
       <c r="C19" s="33" t="n"/>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="B20" s="24">
-        <f>IF(Metas!B20="","",Metas!F20)</f>
+        <f>IF(OR(Metas!B20="",NOT(ISNUMBER(Metas!F20))),"",Metas!F20)</f>
         <v/>
       </c>
       <c r="C20" s="33" t="n"/>
@@ -3628,7 +3628,7 @@
         <v/>
       </c>
       <c r="B21" s="24">
-        <f>IF(Metas!B21="","",Metas!F21)</f>
+        <f>IF(OR(Metas!B21="",NOT(ISNUMBER(Metas!F21))),"",Metas!F21)</f>
         <v/>
       </c>
       <c r="C21" s="33" t="n"/>
@@ -3651,7 +3651,7 @@
         <v/>
       </c>
       <c r="B22" s="24">
-        <f>IF(Metas!B22="","",Metas!F22)</f>
+        <f>IF(OR(Metas!B22="",NOT(ISNUMBER(Metas!F22))),"",Metas!F22)</f>
         <v/>
       </c>
       <c r="C22" s="33" t="n"/>
@@ -3674,7 +3674,7 @@
         <v/>
       </c>
       <c r="B23" s="24">
-        <f>IF(Metas!B23="","",Metas!F23)</f>
+        <f>IF(OR(Metas!B23="",NOT(ISNUMBER(Metas!F23))),"",Metas!F23)</f>
         <v/>
       </c>
       <c r="C23" s="33" t="n"/>
@@ -3697,7 +3697,7 @@
         <v/>
       </c>
       <c r="B24" s="24">
-        <f>IF(Metas!B24="","",Metas!F24)</f>
+        <f>IF(OR(Metas!B24="",NOT(ISNUMBER(Metas!F24))),"",Metas!F24)</f>
         <v/>
       </c>
       <c r="C24" s="33" t="n"/>
@@ -3803,7 +3803,7 @@
         <v>Fechar 3 contratos mensais novos</v>
       </c>
       <c r="B5" s="24">
-        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!F5))),"",Metas!F5)</f>
         <v>3</v>
       </c>
       <c r="C5" s="24">
@@ -3819,11 +3819,11 @@
         <v>2</v>
       </c>
       <c r="F5" s="24">
-        <f>IF(OR(Metas!B5="",E5=""),"",E5-IFERROR(Metas!E5,0))</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(E5)),NOT(ISNUMBER(Metas!E5))),"",E5-Metas!E5)</f>
         <v>2</v>
       </c>
       <c r="G5" s="24">
-        <f>IF(OR(Metas!B5="",E5=""),"",Metas!F5-E5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(E5)),NOT(ISNUMBER(Metas!F5))),"",Metas!F5-E5)</f>
         <v>1</v>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
         <v>Receita recorrente mensal de R$ 30 mil</v>
       </c>
       <c r="B6" s="24">
-        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!F6))),"",Metas!F6)</f>
         <v>30000</v>
       </c>
       <c r="C6" s="24">
@@ -3849,11 +3849,11 @@
         <v>27400</v>
       </c>
       <c r="F6" s="24">
-        <f>IF(OR(Metas!B6="",E6=""),"",E6-IFERROR(Metas!E6,0))</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(E6)),NOT(ISNUMBER(Metas!E6))),"",E6-Metas!E6)</f>
         <v>9400</v>
       </c>
       <c r="G6" s="24">
-        <f>IF(OR(Metas!B6="",E6=""),"",Metas!F6-E6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(E6)),NOT(ISNUMBER(Metas!F6))),"",Metas!F6-E6)</f>
         <v>2600</v>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
         <v>Propostas enviadas no trimestre</v>
       </c>
       <c r="B7" s="24">
-        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!F7))),"",Metas!F7)</f>
         <v>24</v>
       </c>
       <c r="C7" s="24">
@@ -3879,11 +3879,11 @@
         <v>24</v>
       </c>
       <c r="F7" s="24">
-        <f>IF(OR(Metas!B7="",E7=""),"",E7-IFERROR(Metas!E7,0))</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(E7)),NOT(ISNUMBER(Metas!E7))),"",E7-Metas!E7)</f>
         <v>24</v>
       </c>
       <c r="G7" s="24">
-        <f>IF(OR(Metas!B7="",E7=""),"",Metas!F7-E7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(E7)),NOT(ISNUMBER(Metas!F7))),"",Metas!F7-E7)</f>
         <v>0</v>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
         <v/>
       </c>
       <c r="B8" s="24">
-        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!F8))),"",Metas!F8)</f>
         <v/>
       </c>
       <c r="C8" s="24">
@@ -3909,11 +3909,11 @@
         <v/>
       </c>
       <c r="F8" s="24">
-        <f>IF(OR(Metas!B8="",E8=""),"",E8-IFERROR(Metas!E8,0))</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(E8)),NOT(ISNUMBER(Metas!E8))),"",E8-Metas!E8)</f>
         <v/>
       </c>
       <c r="G8" s="24">
-        <f>IF(OR(Metas!B8="",E8=""),"",Metas!F8-E8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(E8)),NOT(ISNUMBER(Metas!F8))),"",Metas!F8-E8)</f>
         <v/>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>Etapas atrasadas por semana (média)</v>
       </c>
       <c r="B9" s="24">
-        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!F9))),"",Metas!F9)</f>
         <v>1</v>
       </c>
       <c r="C9" s="24">
@@ -3939,11 +3939,11 @@
         <v>3</v>
       </c>
       <c r="F9" s="24">
-        <f>IF(OR(Metas!B9="",E9=""),"",E9-IFERROR(Metas!E9,0))</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(E9)),NOT(ISNUMBER(Metas!E9))),"",E9-Metas!E9)</f>
         <v>-1</v>
       </c>
       <c r="G9" s="24">
-        <f>IF(OR(Metas!B9="",E9=""),"",Metas!F9-E9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(E9)),NOT(ISNUMBER(Metas!F9))),"",Metas!F9-E9)</f>
         <v>-2</v>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
         <v>Projetos entregues na data combinada</v>
       </c>
       <c r="B10" s="24">
-        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!F10))),"",Metas!F10)</f>
         <v>90</v>
       </c>
       <c r="C10" s="24">
@@ -3969,11 +3969,11 @@
         <v>82</v>
       </c>
       <c r="F10" s="24">
-        <f>IF(OR(Metas!B10="",E10=""),"",E10-IFERROR(Metas!E10,0))</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(E10)),NOT(ISNUMBER(Metas!E10))),"",E10-Metas!E10)</f>
         <v>22</v>
       </c>
       <c r="G10" s="24">
-        <f>IF(OR(Metas!B10="",E10=""),"",Metas!F10-E10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(E10)),NOT(ISNUMBER(Metas!F10))),"",Metas!F10-E10)</f>
         <v>8</v>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="B11" s="24">
-        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!F11))),"",Metas!F11)</f>
         <v/>
       </c>
       <c r="C11" s="24">
@@ -3999,11 +3999,11 @@
         <v/>
       </c>
       <c r="F11" s="24">
-        <f>IF(OR(Metas!B11="",E11=""),"",E11-IFERROR(Metas!E11,0))</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(E11)),NOT(ISNUMBER(Metas!E11))),"",E11-Metas!E11)</f>
         <v/>
       </c>
       <c r="G11" s="24">
-        <f>IF(OR(Metas!B11="",E11=""),"",Metas!F11-E11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(E11)),NOT(ISNUMBER(Metas!F11))),"",Metas!F11-E11)</f>
         <v/>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
         <v/>
       </c>
       <c r="B12" s="24">
-        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!F12))),"",Metas!F12)</f>
         <v/>
       </c>
       <c r="C12" s="24">
@@ -4029,11 +4029,11 @@
         <v/>
       </c>
       <c r="F12" s="24">
-        <f>IF(OR(Metas!B12="",E12=""),"",E12-IFERROR(Metas!E12,0))</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(E12)),NOT(ISNUMBER(Metas!E12))),"",E12-Metas!E12)</f>
         <v/>
       </c>
       <c r="G12" s="24">
-        <f>IF(OR(Metas!B12="",E12=""),"",Metas!F12-E12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(E12)),NOT(ISNUMBER(Metas!F12))),"",Metas!F12-E12)</f>
         <v/>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
         <v>Rodadas de revisão por peça (média)</v>
       </c>
       <c r="B13" s="24">
-        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!F13))),"",Metas!F13)</f>
         <v>2</v>
       </c>
       <c r="C13" s="24">
@@ -4059,11 +4059,11 @@
         <v>2.8</v>
       </c>
       <c r="F13" s="24">
-        <f>IF(OR(Metas!B13="",E13=""),"",E13-IFERROR(Metas!E13,0))</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(E13)),NOT(ISNUMBER(Metas!E13))),"",E13-Metas!E13)</f>
         <v>-0.4</v>
       </c>
       <c r="G13" s="24">
-        <f>IF(OR(Metas!B13="",E13=""),"",Metas!F13-E13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(E13)),NOT(ISNUMBER(Metas!F13))),"",Metas!F13-E13)</f>
         <v>-0.8</v>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>Peças aprovadas de primeira</v>
       </c>
       <c r="B14" s="24">
-        <f>IF(Metas!B14="","",Metas!F14)</f>
+        <f>IF(OR(Metas!B14="",NOT(ISNUMBER(Metas!F14))),"",Metas!F14)</f>
         <v>65</v>
       </c>
       <c r="C14" s="24">
@@ -4089,11 +4089,11 @@
         <v>60</v>
       </c>
       <c r="F14" s="24">
-        <f>IF(OR(Metas!B14="",E14=""),"",E14-IFERROR(Metas!E14,0))</f>
+        <f>IF(OR(Metas!B14="",NOT(ISNUMBER(E14)),NOT(ISNUMBER(Metas!E14))),"",E14-Metas!E14)</f>
         <v>20</v>
       </c>
       <c r="G14" s="24">
-        <f>IF(OR(Metas!B14="",E14=""),"",Metas!F14-E14)</f>
+        <f>IF(OR(Metas!B14="",NOT(ISNUMBER(E14)),NOT(ISNUMBER(Metas!F14))),"",Metas!F14-E14)</f>
         <v>5</v>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
         <v/>
       </c>
       <c r="B15" s="24">
-        <f>IF(Metas!B15="","",Metas!F15)</f>
+        <f>IF(OR(Metas!B15="",NOT(ISNUMBER(Metas!F15))),"",Metas!F15)</f>
         <v/>
       </c>
       <c r="C15" s="24">
@@ -4119,11 +4119,11 @@
         <v/>
       </c>
       <c r="F15" s="24">
-        <f>IF(OR(Metas!B15="",E15=""),"",E15-IFERROR(Metas!E15,0))</f>
+        <f>IF(OR(Metas!B15="",NOT(ISNUMBER(E15)),NOT(ISNUMBER(Metas!E15))),"",E15-Metas!E15)</f>
         <v/>
       </c>
       <c r="G15" s="24">
-        <f>IF(OR(Metas!B15="",E15=""),"",Metas!F15-E15)</f>
+        <f>IF(OR(Metas!B15="",NOT(ISNUMBER(E15)),NOT(ISNUMBER(Metas!F15))),"",Metas!F15-E15)</f>
         <v/>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
         <v/>
       </c>
       <c r="B16" s="24">
-        <f>IF(Metas!B16="","",Metas!F16)</f>
+        <f>IF(OR(Metas!B16="",NOT(ISNUMBER(Metas!F16))),"",Metas!F16)</f>
         <v/>
       </c>
       <c r="C16" s="24">
@@ -4149,11 +4149,11 @@
         <v/>
       </c>
       <c r="F16" s="24">
-        <f>IF(OR(Metas!B16="",E16=""),"",E16-IFERROR(Metas!E16,0))</f>
+        <f>IF(OR(Metas!B16="",NOT(ISNUMBER(E16)),NOT(ISNUMBER(Metas!E16))),"",E16-Metas!E16)</f>
         <v/>
       </c>
       <c r="G16" s="24">
-        <f>IF(OR(Metas!B16="",E16=""),"",Metas!F16-E16)</f>
+        <f>IF(OR(Metas!B16="",NOT(ISNUMBER(E16)),NOT(ISNUMBER(Metas!F16))),"",Metas!F16-E16)</f>
         <v/>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
         <v>Relatório mensal enviado até o dia 5</v>
       </c>
       <c r="B17" s="24">
-        <f>IF(Metas!B17="","",Metas!F17)</f>
+        <f>IF(OR(Metas!B17="",NOT(ISNUMBER(Metas!F17))),"",Metas!F17)</f>
         <v>3</v>
       </c>
       <c r="C17" s="24">
@@ -4179,11 +4179,11 @@
         <v>2</v>
       </c>
       <c r="F17" s="24">
-        <f>IF(OR(Metas!B17="",E17=""),"",E17-IFERROR(Metas!E17,0))</f>
+        <f>IF(OR(Metas!B17="",NOT(ISNUMBER(E17)),NOT(ISNUMBER(Metas!E17))),"",E17-Metas!E17)</f>
         <v>2</v>
       </c>
       <c r="G17" s="24">
-        <f>IF(OR(Metas!B17="",E17=""),"",Metas!F17-E17)</f>
+        <f>IF(OR(Metas!B17="",NOT(ISNUMBER(E17)),NOT(ISNUMBER(Metas!F17))),"",Metas!F17-E17)</f>
         <v>1</v>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
         <v>Horas extras da equipe no mês</v>
       </c>
       <c r="B18" s="24">
-        <f>IF(Metas!B18="","",Metas!F18)</f>
+        <f>IF(OR(Metas!B18="",NOT(ISNUMBER(Metas!F18))),"",Metas!F18)</f>
         <v>8</v>
       </c>
       <c r="C18" s="24">
@@ -4209,11 +4209,11 @@
         <v>14</v>
       </c>
       <c r="F18" s="24">
-        <f>IF(OR(Metas!B18="",E18=""),"",E18-IFERROR(Metas!E18,0))</f>
+        <f>IF(OR(Metas!B18="",NOT(ISNUMBER(E18)),NOT(ISNUMBER(Metas!E18))),"",E18-Metas!E18)</f>
         <v>-6</v>
       </c>
       <c r="G18" s="24">
-        <f>IF(OR(Metas!B18="",E18=""),"",Metas!F18-E18)</f>
+        <f>IF(OR(Metas!B18="",NOT(ISNUMBER(E18)),NOT(ISNUMBER(Metas!F18))),"",Metas!F18-E18)</f>
         <v>-6</v>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
         <v/>
       </c>
       <c r="B19" s="24">
-        <f>IF(Metas!B19="","",Metas!F19)</f>
+        <f>IF(OR(Metas!B19="",NOT(ISNUMBER(Metas!F19))),"",Metas!F19)</f>
         <v/>
       </c>
       <c r="C19" s="24">
@@ -4239,11 +4239,11 @@
         <v/>
       </c>
       <c r="F19" s="24">
-        <f>IF(OR(Metas!B19="",E19=""),"",E19-IFERROR(Metas!E19,0))</f>
+        <f>IF(OR(Metas!B19="",NOT(ISNUMBER(E19)),NOT(ISNUMBER(Metas!E19))),"",E19-Metas!E19)</f>
         <v/>
       </c>
       <c r="G19" s="24">
-        <f>IF(OR(Metas!B19="",E19=""),"",Metas!F19-E19)</f>
+        <f>IF(OR(Metas!B19="",NOT(ISNUMBER(E19)),NOT(ISNUMBER(Metas!F19))),"",Metas!F19-E19)</f>
         <v/>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
         <v/>
       </c>
       <c r="B20" s="24">
-        <f>IF(Metas!B20="","",Metas!F20)</f>
+        <f>IF(OR(Metas!B20="",NOT(ISNUMBER(Metas!F20))),"",Metas!F20)</f>
         <v/>
       </c>
       <c r="C20" s="24">
@@ -4269,11 +4269,11 @@
         <v/>
       </c>
       <c r="F20" s="24">
-        <f>IF(OR(Metas!B20="",E20=""),"",E20-IFERROR(Metas!E20,0))</f>
+        <f>IF(OR(Metas!B20="",NOT(ISNUMBER(E20)),NOT(ISNUMBER(Metas!E20))),"",E20-Metas!E20)</f>
         <v/>
       </c>
       <c r="G20" s="24">
-        <f>IF(OR(Metas!B20="",E20=""),"",Metas!F20-E20)</f>
+        <f>IF(OR(Metas!B20="",NOT(ISNUMBER(E20)),NOT(ISNUMBER(Metas!F20))),"",Metas!F20-E20)</f>
         <v/>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
         <v/>
       </c>
       <c r="B21" s="24">
-        <f>IF(Metas!B21="","",Metas!F21)</f>
+        <f>IF(OR(Metas!B21="",NOT(ISNUMBER(Metas!F21))),"",Metas!F21)</f>
         <v/>
       </c>
       <c r="C21" s="24">
@@ -4299,11 +4299,11 @@
         <v/>
       </c>
       <c r="F21" s="24">
-        <f>IF(OR(Metas!B21="",E21=""),"",E21-IFERROR(Metas!E21,0))</f>
+        <f>IF(OR(Metas!B21="",NOT(ISNUMBER(E21)),NOT(ISNUMBER(Metas!E21))),"",E21-Metas!E21)</f>
         <v/>
       </c>
       <c r="G21" s="24">
-        <f>IF(OR(Metas!B21="",E21=""),"",Metas!F21-E21)</f>
+        <f>IF(OR(Metas!B21="",NOT(ISNUMBER(E21)),NOT(ISNUMBER(Metas!F21))),"",Metas!F21-E21)</f>
         <v/>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
         <v/>
       </c>
       <c r="B22" s="24">
-        <f>IF(Metas!B22="","",Metas!F22)</f>
+        <f>IF(OR(Metas!B22="",NOT(ISNUMBER(Metas!F22))),"",Metas!F22)</f>
         <v/>
       </c>
       <c r="C22" s="24">
@@ -4329,11 +4329,11 @@
         <v/>
       </c>
       <c r="F22" s="24">
-        <f>IF(OR(Metas!B22="",E22=""),"",E22-IFERROR(Metas!E22,0))</f>
+        <f>IF(OR(Metas!B22="",NOT(ISNUMBER(E22)),NOT(ISNUMBER(Metas!E22))),"",E22-Metas!E22)</f>
         <v/>
       </c>
       <c r="G22" s="24">
-        <f>IF(OR(Metas!B22="",E22=""),"",Metas!F22-E22)</f>
+        <f>IF(OR(Metas!B22="",NOT(ISNUMBER(E22)),NOT(ISNUMBER(Metas!F22))),"",Metas!F22-E22)</f>
         <v/>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
         <v/>
       </c>
       <c r="B23" s="24">
-        <f>IF(Metas!B23="","",Metas!F23)</f>
+        <f>IF(OR(Metas!B23="",NOT(ISNUMBER(Metas!F23))),"",Metas!F23)</f>
         <v/>
       </c>
       <c r="C23" s="24">
@@ -4359,11 +4359,11 @@
         <v/>
       </c>
       <c r="F23" s="24">
-        <f>IF(OR(Metas!B23="",E23=""),"",E23-IFERROR(Metas!E23,0))</f>
+        <f>IF(OR(Metas!B23="",NOT(ISNUMBER(E23)),NOT(ISNUMBER(Metas!E23))),"",E23-Metas!E23)</f>
         <v/>
       </c>
       <c r="G23" s="24">
-        <f>IF(OR(Metas!B23="",E23=""),"",Metas!F23-E23)</f>
+        <f>IF(OR(Metas!B23="",NOT(ISNUMBER(E23)),NOT(ISNUMBER(Metas!F23))),"",Metas!F23-E23)</f>
         <v/>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
         <v/>
       </c>
       <c r="B24" s="24">
-        <f>IF(Metas!B24="","",Metas!F24)</f>
+        <f>IF(OR(Metas!B24="",NOT(ISNUMBER(Metas!F24))),"",Metas!F24)</f>
         <v/>
       </c>
       <c r="C24" s="24">
@@ -4389,11 +4389,11 @@
         <v/>
       </c>
       <c r="F24" s="24">
-        <f>IF(OR(Metas!B24="",E24=""),"",E24-IFERROR(Metas!E24,0))</f>
+        <f>IF(OR(Metas!B24="",NOT(ISNUMBER(E24)),NOT(ISNUMBER(Metas!E24))),"",E24-Metas!E24)</f>
         <v/>
       </c>
       <c r="G24" s="24">
-        <f>IF(OR(Metas!B24="",E24=""),"",Metas!F24-E24)</f>
+        <f>IF(OR(Metas!B24="",NOT(ISNUMBER(E24)),NOT(ISNUMBER(Metas!F24))),"",Metas!F24-E24)</f>
         <v/>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -1289,7 +1289,7 @@
         <v>Fechar 3 contratos mensais novos</v>
       </c>
       <c r="B17" s="24" t="str">
-        <f>IF(Metas!B5="","",Metas!C5)</f>
+        <f>IF(OR(Metas!B5="",Metas!C5=""),"",Metas!C5)</f>
         <v>Ana</v>
       </c>
       <c r="C17" s="27">
@@ -1323,7 +1323,7 @@
         <v>Receita recorrente mensal de R$ 30 mil</v>
       </c>
       <c r="B18" s="24" t="str">
-        <f>IF(Metas!B6="","",Metas!C6)</f>
+        <f>IF(OR(Metas!B6="",Metas!C6=""),"",Metas!C6)</f>
         <v>Ana</v>
       </c>
       <c r="C18" s="27">
@@ -1357,7 +1357,7 @@
         <v>Propostas enviadas no trimestre</v>
       </c>
       <c r="B19" s="24" t="str">
-        <f>IF(Metas!B7="","",Metas!C7)</f>
+        <f>IF(OR(Metas!B7="",Metas!C7=""),"",Metas!C7)</f>
         <v>Carla</v>
       </c>
       <c r="C19" s="27">
@@ -1391,7 +1391,7 @@
         <v/>
       </c>
       <c r="B20" s="24">
-        <f>IF(Metas!B8="","",Metas!C8)</f>
+        <f>IF(OR(Metas!B8="",Metas!C8=""),"",Metas!C8)</f>
         <v/>
       </c>
       <c r="C20" s="27">
@@ -1425,7 +1425,7 @@
         <v>Etapas atrasadas por semana (média)</v>
       </c>
       <c r="B21" s="24" t="str">
-        <f>IF(Metas!B9="","",Metas!C9)</f>
+        <f>IF(OR(Metas!B9="",Metas!C9=""),"",Metas!C9)</f>
         <v>Ana</v>
       </c>
       <c r="C21" s="27">
@@ -1459,7 +1459,7 @@
         <v>Projetos entregues na data combinada</v>
       </c>
       <c r="B22" s="24" t="str">
-        <f>IF(Metas!B10="","",Metas!C10)</f>
+        <f>IF(OR(Metas!B10="",Metas!C10=""),"",Metas!C10)</f>
         <v>Bruno</v>
       </c>
       <c r="C22" s="27">
@@ -1493,7 +1493,7 @@
         <v/>
       </c>
       <c r="B23" s="24">
-        <f>IF(Metas!B11="","",Metas!C11)</f>
+        <f>IF(OR(Metas!B11="",Metas!C11=""),"",Metas!C11)</f>
         <v/>
       </c>
       <c r="C23" s="27">
@@ -1527,7 +1527,7 @@
         <v/>
       </c>
       <c r="B24" s="24">
-        <f>IF(Metas!B12="","",Metas!C12)</f>
+        <f>IF(OR(Metas!B12="",Metas!C12=""),"",Metas!C12)</f>
         <v/>
       </c>
       <c r="C24" s="27">
@@ -1561,7 +1561,7 @@
         <v>Rodadas de revisão por peça (média)</v>
       </c>
       <c r="B25" s="24" t="str">
-        <f>IF(Metas!B13="","",Metas!C13)</f>
+        <f>IF(OR(Metas!B13="",Metas!C13=""),"",Metas!C13)</f>
         <v>Bruno</v>
       </c>
       <c r="C25" s="27">
@@ -1595,7 +1595,7 @@
         <v>Peças aprovadas de primeira</v>
       </c>
       <c r="B26" s="24" t="str">
-        <f>IF(Metas!B14="","",Metas!C14)</f>
+        <f>IF(OR(Metas!B14="",Metas!C14=""),"",Metas!C14)</f>
         <v>Carla</v>
       </c>
       <c r="C26" s="27">
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="B27" s="24">
-        <f>IF(Metas!B15="","",Metas!C15)</f>
+        <f>IF(OR(Metas!B15="",Metas!C15=""),"",Metas!C15)</f>
         <v/>
       </c>
       <c r="C27" s="27">
@@ -1663,7 +1663,7 @@
         <v/>
       </c>
       <c r="B28" s="24">
-        <f>IF(Metas!B16="","",Metas!C16)</f>
+        <f>IF(OR(Metas!B16="",Metas!C16=""),"",Metas!C16)</f>
         <v/>
       </c>
       <c r="C28" s="27">
@@ -1697,7 +1697,7 @@
         <v>Relatório mensal enviado até o dia 5</v>
       </c>
       <c r="B29" s="24" t="str">
-        <f>IF(Metas!B17="","",Metas!C17)</f>
+        <f>IF(OR(Metas!B17="",Metas!C17=""),"",Metas!C17)</f>
         <v>Ana</v>
       </c>
       <c r="C29" s="27">
@@ -1731,7 +1731,7 @@
         <v>Horas extras da equipe no mês</v>
       </c>
       <c r="B30" s="24" t="str">
-        <f>IF(Metas!B18="","",Metas!C18)</f>
+        <f>IF(OR(Metas!B18="",Metas!C18=""),"",Metas!C18)</f>
         <v>Ana</v>
       </c>
       <c r="C30" s="27">
@@ -1765,7 +1765,7 @@
         <v/>
       </c>
       <c r="B31" s="24">
-        <f>IF(Metas!B19="","",Metas!C19)</f>
+        <f>IF(OR(Metas!B19="",Metas!C19=""),"",Metas!C19)</f>
         <v/>
       </c>
       <c r="C31" s="27">
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="B32" s="24">
-        <f>IF(Metas!B20="","",Metas!C20)</f>
+        <f>IF(OR(Metas!B20="",Metas!C20=""),"",Metas!C20)</f>
         <v/>
       </c>
       <c r="C32" s="27">
@@ -1833,7 +1833,7 @@
         <v/>
       </c>
       <c r="B33" s="24">
-        <f>IF(Metas!B21="","",Metas!C21)</f>
+        <f>IF(OR(Metas!B21="",Metas!C21=""),"",Metas!C21)</f>
         <v/>
       </c>
       <c r="C33" s="27">
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="B34" s="24">
-        <f>IF(Metas!B22="","",Metas!C22)</f>
+        <f>IF(OR(Metas!B22="",Metas!C22=""),"",Metas!C22)</f>
         <v/>
       </c>
       <c r="C34" s="27">
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="B35" s="24">
-        <f>IF(Metas!B23="","",Metas!C23)</f>
+        <f>IF(OR(Metas!B23="",Metas!C23=""),"",Metas!C23)</f>
         <v/>
       </c>
       <c r="C35" s="27">
@@ -1935,7 +1935,7 @@
         <v/>
       </c>
       <c r="B36" s="24">
-        <f>IF(Metas!B24="","",Metas!C24)</f>
+        <f>IF(OR(Metas!B24="",Metas!C24=""),"",Metas!C24)</f>
         <v/>
       </c>
       <c r="C36" s="27">

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/06-metas-do-trimestre.xlsx
@@ -812,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -928,7 +929,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
